--- a/tame_output/ON/bt/strategyON_20240728.xlsx
+++ b/tame_output/ON/bt/strategyON_20240728.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.3%</t>
+          <t>111.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.0%</t>
+          <t>454.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-657.0%</t>
+          <t>-656.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-191.5%</t>
+          <t>-191.2%</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-210.1%</t>
+          <t>-209.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-54.8%</t>
+          <t>-54.2%</t>
         </is>
       </c>
     </row>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321018</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636282</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959853</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782703</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632632</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647104</v>
+        <v>3.754911907647102</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301342</v>
+        <v>3.652163313301341</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215467</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253286</v>
+        <v>3.750058176253285</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78364702771783</v>
+        <v>3.783647027717829</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616947</v>
+        <v>3.798310944616946</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085619</v>
+        <v>3.825767093085618</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.199006504188853</v>
+        <v>-5.300063251025478</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.681440347716604</v>
+        <v>1.641017648981954</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1832521864234846</v>
+        <v>0.08219543958685932</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.871350685559984</v>
+        <v>3.810716637458008</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462781</v>
+        <v>3.80470312146278</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.329587238719696</v>
+        <v>-5.430643985556321</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.632710097978231</v>
+        <v>1.592287399243581</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.05267145189264211</v>
+        <v>-0.04838529494398319</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.796504288915441</v>
+        <v>3.735870240813466</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218599</v>
+        <v>3.775043021218598</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.165090904528734</v>
+        <v>-5.266147651365359</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.682935450730698</v>
+        <v>1.642512751996048</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.05267145189264211</v>
+        <v>-0.04838529494398319</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.780931107991524</v>
+        <v>3.720297059889549</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.040610423804782</v>
+        <v>-5.141667170641408</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.731915353456708</v>
+        <v>1.691492654722058</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.05267145189264211</v>
+        <v>-0.04838529494398319</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.780118818427954</v>
+        <v>3.719484770325979</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533049</v>
+        <v>3.83232118453305</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.050995618694672</v>
+        <v>-5.152052365531297</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.737630054625825</v>
+        <v>1.697207355891175</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.04228625700275279</v>
+        <v>-0.05877048983387251</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.783756480619093</v>
+        <v>3.723122432517118</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.813240087881066</v>
+        <v>3.751405511369286</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.954415384160248</v>
+        <v>-4.945395277289673</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.84709915421602</v>
+        <v>1.85070719696425</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1388664915371772</v>
+        <v>0.1478865984077524</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.912541627116172</v>
+        <v>3.917953691238518</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240728.xlsx
+++ b/tame_output/ON/bt/strategyON_20240728.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>24.7%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.5%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.2%</t>
+          <t>451.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-656.1%</t>
+          <t>-682.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24649.4%</t>
+          <t>-24645.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-191.2%</t>
+          <t>-201.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-209.2%</t>
+          <t>-210.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-54.2%</t>
+          <t>-55.1%</t>
         </is>
       </c>
     </row>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.835835482065201</v>
+        <v>-8.087670299355949</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.01642573307558548</v>
+        <v>-0.08430819384071375</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.314228376767125</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.79565118369901</v>
+        <v>-8.047486000989759</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.03284307630990302</v>
+        <v>-0.06789085060639621</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.274044078400934</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.632251312759648</v>
+        <v>-7.884086130050396</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.09756984590640494</v>
+        <v>-0.003164081009894293</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.110644207461571</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.398770090530049</v>
+        <v>-7.650604907820798</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1988867636360969</v>
+        <v>0.09815283671979724</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.8771629852319727</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.249103699522534</v>
+        <v>-7.500938516813282</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2558611097261436</v>
+        <v>0.1551271828098444</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7842594939894367</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.116828225891648</v>
+        <v>-7.368663043182396</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3041387859255251</v>
+        <v>0.2034048590092259</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.6519840203585501</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.961089893331906</v>
+        <v>-7.212924710622654</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3692491796370589</v>
+        <v>0.2685152527207593</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4962456877988085</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.712090094648325</v>
+        <v>-6.963924911939073</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4817554403341497</v>
+        <v>0.3810215134178505</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2472458891152278</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.817680084421429</v>
+        <v>-7.069514901712178</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3115435148256895</v>
+        <v>0.2108095879093899</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3528358788883322</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.836414986540026</v>
+        <v>-7.088249803830775</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3525938958553372</v>
+        <v>0.2518599689390375</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3584318885484635</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.688474945132427</v>
+        <v>-6.940309762423175</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2918909897302093</v>
+        <v>0.1911570628139097</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.3381109726399059</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.635505422878438</v>
+        <v>-6.887340240169187</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3043648123783265</v>
+        <v>0.2036308854620268</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.285141450385917</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.591957016107748</v>
+        <v>-6.843791833398496</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3148235629915095</v>
+        <v>0.2140896360752098</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.285141450385917</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.558593809628979</v>
+        <v>-6.810428626919728</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3426311999641598</v>
+        <v>0.2418972730478606</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.285141450385917</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.450334672506457</v>
+        <v>-6.702169489797206</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3804669752723635</v>
+        <v>0.2797330483560643</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.285141450385917</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.327043537689327</v>
+        <v>-6.578878354980075</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4272815232097931</v>
+        <v>0.3265475962934934</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.1618503155687865</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.305894338785883</v>
+        <v>-6.557729156076632</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4434421810084954</v>
+        <v>0.3427082540921962</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.1407011166653432</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.062128896802439</v>
+        <v>-6.313963714093187</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5367290661489239</v>
+        <v>0.4359951392326242</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.1407011166653432</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.960366076525144</v>
+        <v>-6.212200893815893</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5795585081798578</v>
+        <v>0.4788245812635585</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.1274820482729145</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.710515682576069</v>
+        <v>-5.962350499866818</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6722407407431898</v>
+        <v>0.5715068138268906</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.1274820482729145</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.534623590108637</v>
+        <v>-5.786458407399385</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7461967012508115</v>
+        <v>0.6454627743345123</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.1274820482729145</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.363177127086174</v>
+        <v>-5.615011944376922</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8281027925143505</v>
+        <v>0.7273688655980513</v>
       </c>
       <c r="F1921" t="n">
         <v>0.04396441474954865</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.288887561347835</v>
+        <v>-5.540722378638582</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8568390964259831</v>
+        <v>0.7561051695096839</v>
       </c>
       <c r="F1922" t="n">
         <v>0.1182539804878879</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.2252518191139</v>
+        <v>-5.477086636404648</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.886988194373874</v>
+        <v>0.7862542674575752</v>
       </c>
       <c r="F1923" t="n">
         <v>0.1818897227218225</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.11382505978798</v>
+        <v>-5.365659877078728</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.912753156888038</v>
+        <v>0.8120192299717388</v>
       </c>
       <c r="F1924" t="n">
         <v>0.1818897227218225</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.124327682853269</v>
+        <v>-5.376162500144017</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9102951842867997</v>
+        <v>0.8095612573705004</v>
       </c>
       <c r="F1925" t="n">
         <v>0.1713870996565336</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.052085114682074</v>
+        <v>-5.303919931972822</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9431215253900977</v>
+        <v>0.8423875984737985</v>
       </c>
       <c r="F1926" t="n">
         <v>0.1713870996565336</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.034371427804209</v>
+        <v>-5.286206245094957</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9508855840585837</v>
+        <v>0.8501516571422849</v>
       </c>
       <c r="F1927" t="n">
         <v>0.1745684285534504</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.925566542324482</v>
+        <v>-5.17740135961523</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9914056094704682</v>
+        <v>0.890671682554169</v>
       </c>
       <c r="F1928" t="n">
         <v>0.1745684285534504</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.705545744287472</v>
+        <v>-4.957380561578219</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.080992965695887</v>
+        <v>0.9802590387795875</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3157882736214306</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.572678055224194</v>
+        <v>-4.824512872514942</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.150034224123021</v>
+        <v>1.049300297206722</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3157882736214306</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.452504971859695</v>
+        <v>-4.704339789150443</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.199249301909122</v>
+        <v>1.098515374992823</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4359613569859296</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.307832826759958</v>
+        <v>-4.559667644050705</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.267206262510457</v>
+        <v>1.166472335594158</v>
       </c>
       <c r="F1932" t="n">
         <v>0.580633502085667</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.36770765411765</v>
+        <v>-4.619542471408398</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.229293822968806</v>
+        <v>1.128559896052507</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5207586747279749</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.247887423206813</v>
+        <v>-4.499722240497561</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.292511084567349</v>
+        <v>1.19177715765105</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5207586747279749</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.250357129668619</v>
+        <v>-4.502191946959367</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.199167401305068</v>
+        <v>1.098433474388769</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5182889682661687</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.318727315992629</v>
+        <v>-4.570562133283377</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.091081188260766</v>
+        <v>0.9903472613444668</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5275646673023836</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.332515368839676</v>
+        <v>-4.584350186130424</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.076002675753838</v>
+        <v>0.9752687488375393</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5275646673023836</v>
@@ -46125,10 +46125,10 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.388035444732266</v>
+        <v>-4.639870262023013</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.190825482089005</v>
+        <v>1.090091555172706</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5275646673023836</v>
@@ -46148,10 +46148,10 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.212561184939796</v>
+        <v>-4.464396002230544</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.265582417997781</v>
+        <v>1.164848491081482</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5275646673023836</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.323497437581045</v>
+        <v>-4.575332254871793</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.196949945702488</v>
+        <v>1.096216018786189</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5275646673023836</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.289833892108763</v>
+        <v>-4.54166870939951</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.138953677292851</v>
+        <v>1.038219750376552</v>
       </c>
       <c r="F1941" t="n">
         <v>0.5612282127746655</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.229981272905039</v>
+        <v>-4.481816090195787</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.173067111406472</v>
+        <v>1.072333184490173</v>
       </c>
       <c r="F1942" t="n">
         <v>0.5612282127746655</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.143737809878662</v>
+        <v>-4.395572627169409</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.202510767190884</v>
+        <v>1.101776840274585</v>
       </c>
       <c r="F1943" t="n">
         <v>0.5612282127746655</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.189044629277642</v>
+        <v>-4.440879446568389</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.176163814875817</v>
+        <v>1.075429887959518</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5204180497654347</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.218077733979943</v>
+        <v>-4.46991255127069</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.165102446027999</v>
+        <v>1.064368519111699</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5204180497654347</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.125267252529083</v>
+        <v>-4.377102069819831</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.131499330499708</v>
+        <v>1.030765403583409</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6132285312162941</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.169656721858511</v>
+        <v>-4.421491539149258</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.115617018692538</v>
+        <v>1.014883091776239</v>
       </c>
       <c r="F1947" t="n">
         <v>0.5688390618868664</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.286198326963853</v>
+        <v>-4.538033144254601</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.064076085162124</v>
+        <v>0.9633421582458248</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4522974567815236</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.17382132578118</v>
+        <v>-4.425656143071928</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.11451818146586</v>
+        <v>1.013784254549561</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4522974567815236</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.201601723682533</v>
+        <v>-4.45343654097328</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.114903224073858</v>
+        <v>1.014169297157559</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4245170588801706</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.319982396412671</v>
+        <v>-4.571817213703419</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9059066749824563</v>
+        <v>0.8051727480661572</v>
       </c>
       <c r="F1951" t="n">
         <v>0.3572992067291944</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.428596474856002</v>
+        <v>-4.68043129214675</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9826107043243293</v>
+        <v>0.8818767774080303</v>
       </c>
       <c r="F1952" t="n">
         <v>0.3572992067291944</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.393187436607859</v>
+        <v>-4.645022253898607</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.01128734572591</v>
+        <v>0.9105534188096105</v>
       </c>
       <c r="F1953" t="n">
         <v>0.3572992067291944</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.354803774049708</v>
+        <v>-4.606638591340456</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.024060252091539</v>
+        <v>0.9233263251752395</v>
       </c>
       <c r="F1954" t="n">
         <v>0.3956828692873455</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.177687444014542</v>
+        <v>-4.42952226130529</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.091635812950907</v>
+        <v>0.9909018860346079</v>
       </c>
       <c r="F1955" t="n">
         <v>0.3956828692873455</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.222779688848088</v>
+        <v>-4.474614506138836</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.074282306779402</v>
+        <v>0.9735483798631028</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3337868261179557</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.04340426760932</v>
+        <v>-4.295239084900068</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.139819450581323</v>
+        <v>1.039085523665024</v>
       </c>
       <c r="F1957" t="n">
         <v>0.4905635842886744</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.088418481129926</v>
+        <v>-4.340253298420674</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.102621220504671</v>
+        <v>1.001887293588372</v>
       </c>
       <c r="F1958" t="n">
         <v>0.4602146889740698</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.355422991402361</v>
+        <v>-4.607257808693109</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.001510978734642</v>
+        <v>0.9007770518183433</v>
       </c>
       <c r="F1959" t="n">
         <v>0.2658516509311212</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.456620772839534</v>
+        <v>-4.708455590130281</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9602357880562749</v>
+        <v>0.8595018611399756</v>
       </c>
       <c r="F1960" t="n">
         <v>0.197442837385802</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.450109806225221</v>
+        <v>-4.701944623515969</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9604401362563166</v>
+        <v>0.8597062093400174</v>
       </c>
       <c r="F1961" t="n">
         <v>0.197442837385802</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.431071678517924</v>
+        <v>-4.682906495808671</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9645801065474804</v>
+        <v>0.8638461796311814</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1392592260546075</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.462198309668542</v>
+        <v>-4.71403312695929</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.071423855721423</v>
+        <v>0.9706899288051243</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1392592260546075</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.47606507100246</v>
+        <v>-4.727899888293208</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.06671048017399</v>
+        <v>0.9659765532576907</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1014013093207846</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789119</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.43126089946253</v>
+        <v>-4.683095716753278</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.090640679186888</v>
+        <v>0.9899067522705887</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1014013093207846</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.283517929227528</v>
+        <v>-4.535352746518275</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.047688088558088</v>
+        <v>0.9469541616417891</v>
       </c>
       <c r="F1966" t="n">
         <v>0.2692086665556677</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.367339150502226</v>
+        <v>-4.619173967792974</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.01695322157969</v>
+        <v>0.9162192946633907</v>
       </c>
       <c r="F1967" t="n">
         <v>0.2692086665556677</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.361186444449442</v>
+        <v>-4.613021261740189</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.020076652392462</v>
+        <v>0.9193427254761628</v>
       </c>
       <c r="F1968" t="n">
         <v>0.275361372608452</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.377995742599944</v>
+        <v>-4.629830559890691</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.012433409872371</v>
+        <v>0.9116994829560723</v>
       </c>
       <c r="F1969" t="n">
         <v>0.2585520744579504</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.315697743823821</v>
+        <v>-4.567532561114569</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.103688163179641</v>
+        <v>1.002954236263342</v>
       </c>
       <c r="F1970" t="n">
         <v>0.2585520744579504</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.113907546158663</v>
+        <v>-4.365742363449411</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9866962439598315</v>
+        <v>0.8859623170435325</v>
       </c>
       <c r="F1971" t="n">
         <v>0.4565702666271048</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.164794258844858</v>
+        <v>-4.416629076135606</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.036631791207529</v>
+        <v>0.9358978642912297</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4056835539409102</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.262534803469832</v>
+        <v>-4.51436962076058</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.012163309473583</v>
+        <v>0.9114293825572837</v>
       </c>
       <c r="F1973" t="n">
         <v>0.38979427580793</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.322744101475117</v>
+        <v>-4.574578918765865</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9866155710961404</v>
+        <v>0.8858816441798414</v>
       </c>
       <c r="F1974" t="n">
         <v>0.3295849778026455</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.246322055043191</v>
+        <v>-4.498156872333938</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.01567600770884</v>
+        <v>0.9149420807925406</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3295849778026455</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316244</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.201948923404622</v>
+        <v>-4.45378374069537</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.033288127799703</v>
+        <v>0.9325542008834042</v>
       </c>
       <c r="F1976" t="n">
         <v>0.3739581094412141</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.224429274263507</v>
+        <v>-4.476264091554254</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.01868978159474</v>
+        <v>0.9179558546784408</v>
       </c>
       <c r="F1977" t="n">
         <v>0.3739581094412141</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.176773543702451</v>
+        <v>-4.428608360993199</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.044133830846967</v>
+        <v>0.9433999039306677</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4216138400022698</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569613</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.076255385203696</v>
+        <v>-4.328090202494444</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.089233467621193</v>
+        <v>0.9884995407048944</v>
       </c>
       <c r="F1979" t="n">
         <v>0.5221319985010243</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.136921975606086</v>
+        <v>-4.388756792896833</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.05172150393611</v>
+        <v>0.9509875770198108</v>
       </c>
       <c r="F1980" t="n">
         <v>0.4404336817824906</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.092083573997687</v>
+        <v>-4.343918391288435</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.073754567190098</v>
+        <v>0.9730206402737989</v>
       </c>
       <c r="F1981" t="n">
         <v>0.4449771147273601</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.111582030239695</v>
+        <v>-4.363416847530443</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.070116124324373</v>
+        <v>0.9693821974080736</v>
       </c>
       <c r="F1982" t="n">
         <v>0.3968924734474558</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405954</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.067379193153795</v>
+        <v>-4.319214010444543</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.09367686168657</v>
+        <v>0.992942934770271</v>
       </c>
       <c r="F1983" t="n">
         <v>0.4410953105333563</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265639</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.104358220817238</v>
+        <v>-4.356193038107985</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.07729525109044</v>
+        <v>0.9765613241741413</v>
       </c>
       <c r="F1984" t="n">
         <v>0.4780692123246868</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.946066803277966</v>
+        <v>-4.197901620568714</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.191859583289189</v>
+        <v>1.09112565637289</v>
       </c>
       <c r="F1985" t="n">
         <v>0.4780692123246868</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321018</v>
+        <v>3.865338681321016</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.738424799643489</v>
+        <v>-3.990259616934237</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.273357089337233</v>
+        <v>1.172623162420933</v>
       </c>
       <c r="F1986" t="n">
         <v>0.685711215959163</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475133</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.687392706920961</v>
+        <v>-3.939227524211709</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.288718154664514</v>
+        <v>1.187984227748215</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7367433086816909</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404848</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.622168525793755</v>
+        <v>-3.874003343084504</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.331995231208101</v>
+        <v>1.231261304291802</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8019674898088965</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.584741505722622</v>
+        <v>-3.83657632301337</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.342927011535835</v>
+        <v>1.242193084619535</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8072190278380782</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.60485316175733</v>
+        <v>-3.856687979048079</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.336139141453192</v>
+        <v>1.235405214536893</v>
       </c>
       <c r="F1990" t="n">
         <v>0.8182463728354974</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636282</v>
+        <v>3.82866144563628</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.551108347330125</v>
+        <v>-3.802943164620874</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.518194838245285</v>
+        <v>1.417460911328985</v>
       </c>
       <c r="F1991" t="n">
         <v>0.8283096822759594</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957619</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.476326086305113</v>
+        <v>-3.728160903595861</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.668220651873107</v>
+        <v>1.567486724956807</v>
       </c>
       <c r="F1992" t="n">
         <v>0.903091943300972</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.450242002041305</v>
+        <v>-3.702076819332053</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.670362261592489</v>
+        <v>1.56962833467619</v>
       </c>
       <c r="F1993" t="n">
         <v>0.903091943300972</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896923</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.372110821192358</v>
+        <v>-3.623945638483106</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.699807929515847</v>
+        <v>1.599074002599548</v>
       </c>
       <c r="F1994" t="n">
         <v>0.9772687541846565</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959853</v>
+        <v>3.796264143959851</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.363218359799075</v>
+        <v>-3.615053177089823</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.720919319799952</v>
+        <v>1.620185392883652</v>
       </c>
       <c r="F1995" t="n">
         <v>0.9772687541846565</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945361</v>
+        <v>3.794424941945359</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.531694476768953</v>
+        <v>-3.783529294059701</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.645383920416585</v>
+        <v>1.544649993500285</v>
       </c>
       <c r="F1996" t="n">
         <v>0.9493209184680758</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782703</v>
+        <v>3.795574066782701</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.833894947907369</v>
+        <v>-3.085729765198118</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.90577342914908</v>
+        <v>1.80503950223278</v>
       </c>
       <c r="F1997" t="n">
         <v>0.8789728590976651</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632632</v>
+        <v>3.78467134563263</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.811173844224217</v>
+        <v>-3.063008661514965</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.905525893119245</v>
+        <v>1.804791966202946</v>
       </c>
       <c r="F1998" t="n">
         <v>0.8789728590976651</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777667</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.940375657518259</v>
+        <v>-3.192210474809008</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.012751293652797</v>
+        <v>1.912017366736498</v>
       </c>
       <c r="F1999" t="n">
         <v>0.7497710458036229</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.095156664296515</v>
+        <v>-3.346991481587263</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.987916713435141</v>
+        <v>1.887182786518842</v>
       </c>
       <c r="F2000" t="n">
         <v>0.7164033717491467</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799959</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.088101974081341</v>
+        <v>-3.33993679137209</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.987413945510756</v>
+        <v>1.886680018594457</v>
       </c>
       <c r="F2001" t="n">
         <v>0.7234580619643205</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331111</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.061150749754853</v>
+        <v>-3.312985567045602</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.008200588886093</v>
+        <v>1.907466661969794</v>
       </c>
       <c r="F2002" t="n">
         <v>0.7383384079920396</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.19710375781117</v>
+        <v>-3.448938575101918</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.137922517808526</v>
+        <v>2.037188590892227</v>
       </c>
       <c r="F2003" t="n">
         <v>0.7383384079920396</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.219511875616042</v>
+        <v>-3.47134669290679</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.12107596558957</v>
+        <v>2.020342038673271</v>
       </c>
       <c r="F2004" t="n">
         <v>0.7383384079920396</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.367517643095441</v>
+        <v>-3.61935246038619</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.063927658147448</v>
+        <v>1.963193731231149</v>
       </c>
       <c r="F2005" t="n">
         <v>0.6516113991284982</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.376958568983971</v>
+        <v>-3.62879338627472</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.116405005513883</v>
+        <v>2.015671078597584</v>
       </c>
       <c r="F2006" t="n">
         <v>0.7740385166718896</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.429232176319613</v>
+        <v>-3.681066993610361</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.098386657124927</v>
+        <v>1.997652730208628</v>
       </c>
       <c r="F2007" t="n">
         <v>0.7217649093362484</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.505562153920518</v>
+        <v>-3.757396971211267</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.065966478978341</v>
+        <v>1.965232552062041</v>
       </c>
       <c r="F2008" t="n">
         <v>0.7217649093362484</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.707815874244872</v>
+        <v>-3.95965069153562</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.979885220451461</v>
+        <v>1.879151293535162</v>
       </c>
       <c r="F2009" t="n">
         <v>0.5195111890118949</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.869384299772127</v>
+        <v>-4.121219117062875</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.913691860450712</v>
+        <v>1.812957933534413</v>
       </c>
       <c r="F2010" t="n">
         <v>0.3927282652140155</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647102</v>
+        <v>3.7549119076471</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.001685591869681</v>
+        <v>-4.253520409160428</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.873844750477609</v>
+        <v>1.77311082356131</v>
       </c>
       <c r="F2011" t="n">
         <v>0.3927282652140155</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763529</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.00324723468454</v>
+        <v>-4.255082051975288</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.873220093351665</v>
+        <v>1.772486166435366</v>
       </c>
       <c r="F2012" t="n">
         <v>0.3927282652140155</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392114</v>
+        <v>3.715834055392112</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.031148021794013</v>
+        <v>-4.28298283908476</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.860583819634878</v>
+        <v>1.759849892718579</v>
       </c>
       <c r="F2013" t="n">
         <v>0.3581313410710807</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172525</v>
+        <v>3.684909939172523</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.153674124496907</v>
+        <v>-4.405508941787654</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.808337822530919</v>
+        <v>1.70760389561462</v>
       </c>
       <c r="F2014" t="n">
         <v>0.2356052383681868</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971076</v>
+        <v>3.619362241971074</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.384188620682496</v>
+        <v>-4.636023437973243</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.782837983647187</v>
+        <v>1.682104056730888</v>
       </c>
       <c r="F2015" t="n">
         <v>0.005090742182598085</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199802</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.640909438677319</v>
+        <v>-4.892744255968067</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.820461375451105</v>
+        <v>1.719727448534806</v>
       </c>
       <c r="F2016" t="n">
         <v>-0.1033238319612167</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622234</v>
+        <v>3.668303164622232</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.79489585645346</v>
+        <v>-5.046730673744207</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.827847077486289</v>
+        <v>1.727113150569989</v>
       </c>
       <c r="F2017" t="n">
         <v>-0.1033238319612167</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808526</v>
+        <v>3.619937176808524</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.744373952625794</v>
+        <v>-4.996208769916541</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.834107041137476</v>
+        <v>1.733373114221177</v>
       </c>
       <c r="F2018" t="n">
         <v>-0.1033238319612167</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.65634689399489</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.996849106633518</v>
+        <v>-5.248683923924266</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.7449874685898</v>
+        <v>1.644253541673501</v>
       </c>
       <c r="F2019" t="n">
         <v>-0.1033238319612167</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.674042696358294</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.266321908555226</v>
+        <v>-5.518156725845974</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.638408882340061</v>
+        <v>1.537674955423761</v>
       </c>
       <c r="F2020" t="n">
         <v>-0.1033238319612167</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637085</v>
+        <v>3.663523617637083</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.423865980284668</v>
+        <v>-5.675700797575415</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.579512995875605</v>
+        <v>1.478779068959306</v>
       </c>
       <c r="F2021" t="n">
         <v>-0.1702256371014912</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301341</v>
+        <v>3.652163313301339</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.701830375867941</v>
+        <v>-5.953665193158689</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.463405090378485</v>
+        <v>1.362671163462186</v>
       </c>
       <c r="F2022" t="n">
         <v>-0.2598453713869755</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215467</v>
+        <v>3.667976467215465</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.818798068506832</v>
+        <v>-6.07063288579758</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.578822070021973</v>
+        <v>1.478088143105674</v>
       </c>
       <c r="F2023" t="n">
         <v>-0.2598453713869755</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69655362845669</v>
+        <v>3.696553628456688</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.903516010727786</v>
+        <v>-6.155350828018533</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.539781531097406</v>
+        <v>1.439047604181107</v>
       </c>
       <c r="F2024" t="n">
         <v>-0.3449614003150219</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253285</v>
+        <v>3.750058176253283</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.985450828996669</v>
+        <v>-6.237285646287416</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.517237021358344</v>
+        <v>1.416503094442044</v>
       </c>
       <c r="F2025" t="n">
         <v>-0.3548961459021021</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717829</v>
+        <v>3.783647027717827</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.931712655596407</v>
+        <v>-6.183547472887154</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.547657929174351</v>
+        <v>1.446924002258052</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.30115797250184</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616946</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.821706372119185</v>
+        <v>-6.073541189409933</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.583813329809415</v>
+        <v>1.483079402893116</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.2779534005845647</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203661</v>
+        <v>3.785578085203659</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.67864679637826</v>
+        <v>-5.930481613669008</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.64528717082776</v>
+        <v>1.54455324391146</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.2699399739945855</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436927</v>
+        <v>3.777251572436925</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.377200070906422</v>
+        <v>-5.62903488819717</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.77312674389903</v>
+        <v>1.672392816982732</v>
       </c>
       <c r="F2029" t="n">
         <v>0.03150675147725179</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064765</v>
+        <v>3.812650101064763</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.401790315141606</v>
+        <v>-5.653625132432354</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.764261823957667</v>
+        <v>1.663527897041368</v>
       </c>
       <c r="F2030" t="n">
         <v>0.03150675147725179</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859299</v>
+        <v>3.821198342859297</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.350751939135086</v>
+        <v>-5.602586756425834</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.785520078740031</v>
+        <v>1.684786151823732</v>
       </c>
       <c r="F2031" t="n">
         <v>0.03150675147725179</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354684</v>
+        <v>3.831748677354682</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.309612644268455</v>
+        <v>-5.561447461559203</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.821013895560828</v>
+        <v>1.72027996864453</v>
       </c>
       <c r="F2032" t="n">
         <v>0.07264604634388261</v>
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085618</v>
+        <v>3.825767093085616</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.300063251025478</v>
+        <v>-5.450841321479601</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.641017648981954</v>
+        <v>1.580706420800305</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.08219543958685932</v>
+        <v>0.1832521864234846</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.810716637458008</v>
+        <v>3.871350685559984</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80470312146278</v>
+        <v>3.804703121462778</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.430643985556321</v>
+        <v>-5.581422056010443</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.592287399243581</v>
+        <v>1.531976171061932</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.04838529494398319</v>
+        <v>0.05267145189264211</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.735870240813466</v>
+        <v>3.796504288915441</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218598</v>
+        <v>3.775043021218596</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.266147651365359</v>
+        <v>-5.416925721819482</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.642512751996048</v>
+        <v>1.582201523814399</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.04838529494398319</v>
+        <v>0.05267145189264211</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.720297059889549</v>
+        <v>3.780931107991524</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462768</v>
+        <v>3.821044820462767</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.141667170641408</v>
+        <v>-5.29244524109553</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.691492654722058</v>
+        <v>1.631181426540409</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.04838529494398319</v>
+        <v>0.05267145189264211</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.719484770325979</v>
+        <v>3.780118818427954</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83232118453305</v>
+        <v>3.832321184533049</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.152052365531297</v>
+        <v>-5.302830435985419</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.697207355891175</v>
+        <v>1.636896127709526</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.05877048983387251</v>
+        <v>0.04228625700275279</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.723122432517118</v>
+        <v>3.783756480619093</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.751405511369286</v>
+        <v>3.527515540589915</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.945395277289673</v>
+        <v>-5.212075959956778</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.85070719696425</v>
+        <v>1.744034923897408</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1478865984077524</v>
+        <v>0.1330407330313945</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.917953691238518</v>
+        <v>3.909046172012703</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240728.xlsx
+++ b/tame_output/ON/bt/strategyON_20240728.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>54.0%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>111.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.0%</t>
+          <t>454.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-682.8%</t>
+          <t>-664.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24645.5%</t>
+          <t>-24649.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-201.8%</t>
+          <t>-194.3%</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.087670299355949</v>
+        <v>-7.835835482065201</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.08430819384071375</v>
+        <v>0.01642573307558548</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.314228376767125</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.047486000989759</v>
+        <v>-7.79565118369901</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.06789085060639621</v>
+        <v>0.03284307630990302</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.274044078400934</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.884086130050396</v>
+        <v>-7.632251312759648</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.003164081009894293</v>
+        <v>0.09756984590640494</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.110644207461571</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.650604907820798</v>
+        <v>-7.398770090530049</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.09815283671979724</v>
+        <v>0.1988867636360969</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.8771629852319727</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.500938516813282</v>
+        <v>-7.249103699522534</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.1551271828098444</v>
+        <v>0.2558611097261436</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7842594939894367</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.368663043182396</v>
+        <v>-7.116828225891648</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2034048590092259</v>
+        <v>0.3041387859255251</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.6519840203585501</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.212924710622654</v>
+        <v>-6.961089893331906</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2685152527207593</v>
+        <v>0.3692491796370589</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4962456877988085</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.963924911939073</v>
+        <v>-6.712090094648325</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3810215134178505</v>
+        <v>0.4817554403341497</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2472458891152278</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.069514901712178</v>
+        <v>-6.817680084421429</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2108095879093899</v>
+        <v>0.3115435148256895</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3528358788883322</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.088249803830775</v>
+        <v>-6.836414986540026</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2518599689390375</v>
+        <v>0.3525938958553372</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3584318885484635</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.940309762423175</v>
+        <v>-6.688474945132427</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1911570628139097</v>
+        <v>0.2918909897302093</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.3381109726399059</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.887340240169187</v>
+        <v>-6.635505422878438</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2036308854620268</v>
+        <v>0.3043648123783265</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.285141450385917</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.843791833398496</v>
+        <v>-6.591957016107748</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2140896360752098</v>
+        <v>0.3148235629915095</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.285141450385917</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.810428626919728</v>
+        <v>-6.558593809628979</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2418972730478606</v>
+        <v>0.3426311999641598</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.285141450385917</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.702169489797206</v>
+        <v>-6.450334672506457</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2797330483560643</v>
+        <v>0.3804669752723635</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.285141450385917</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.578878354980075</v>
+        <v>-6.327043537689327</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3265475962934934</v>
+        <v>0.4272815232097931</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.1618503155687865</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.557729156076632</v>
+        <v>-6.305894338785883</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3427082540921962</v>
+        <v>0.4434421810084954</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.1407011166653432</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.313963714093187</v>
+        <v>-6.062128896802439</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4359951392326242</v>
+        <v>0.5367290661489239</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.1407011166653432</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.212200893815893</v>
+        <v>-5.960366076525144</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4788245812635585</v>
+        <v>0.5795585081798578</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.1274820482729145</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.962350499866818</v>
+        <v>-5.710515682576069</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5715068138268906</v>
+        <v>0.6722407407431898</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.1274820482729145</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.786458407399385</v>
+        <v>-5.534623590108637</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6454627743345123</v>
+        <v>0.7461967012508115</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.1274820482729145</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.615011944376922</v>
+        <v>-5.363177127086174</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7273688655980513</v>
+        <v>0.8281027925143505</v>
       </c>
       <c r="F1921" t="n">
         <v>0.04396441474954865</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.540722378638582</v>
+        <v>-5.288887561347835</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7561051695096839</v>
+        <v>0.8568390964259831</v>
       </c>
       <c r="F1922" t="n">
         <v>0.1182539804878879</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.477086636404648</v>
+        <v>-5.2252518191139</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7862542674575752</v>
+        <v>0.886988194373874</v>
       </c>
       <c r="F1923" t="n">
         <v>0.1818897227218225</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.365659877078728</v>
+        <v>-5.11382505978798</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8120192299717388</v>
+        <v>0.912753156888038</v>
       </c>
       <c r="F1924" t="n">
         <v>0.1818897227218225</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.376162500144017</v>
+        <v>-5.124327682853269</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8095612573705004</v>
+        <v>0.9102951842867997</v>
       </c>
       <c r="F1925" t="n">
         <v>0.1713870996565336</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.303919931972822</v>
+        <v>-5.052085114682074</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8423875984737985</v>
+        <v>0.9431215253900977</v>
       </c>
       <c r="F1926" t="n">
         <v>0.1713870996565336</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879963</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.286206245094957</v>
+        <v>-5.034371427804209</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8501516571422849</v>
+        <v>0.9508855840585837</v>
       </c>
       <c r="F1927" t="n">
         <v>0.1745684285534504</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.17740135961523</v>
+        <v>-4.989951135593245</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.890671682554169</v>
+        <v>0.9656517721629632</v>
       </c>
       <c r="F1928" t="n">
         <v>0.1745684285534504</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.957380561578219</v>
+        <v>-4.769930337556234</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9802590387795875</v>
+        <v>1.055239128388382</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3157882736214306</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.824512872514942</v>
+        <v>-4.637062648492956</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.049300297206722</v>
+        <v>1.124280386815516</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3157882736214306</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.704339789150443</v>
+        <v>-4.516889565128458</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.098515374992823</v>
+        <v>1.173495464601617</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4359613569859296</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.559667644050705</v>
+        <v>-4.37221742002872</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.166472335594158</v>
+        <v>1.241452425202952</v>
       </c>
       <c r="F1932" t="n">
         <v>0.580633502085667</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.619542471408398</v>
+        <v>-4.432092247386413</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.128559896052507</v>
+        <v>1.203539985661301</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5207586747279749</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.499722240497561</v>
+        <v>-4.312272016475576</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.19177715765105</v>
+        <v>1.266757247259844</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5207586747279749</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.502191946959367</v>
+        <v>-4.314741722937382</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.098433474388769</v>
+        <v>1.173413563997563</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5182889682661687</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.570562133283377</v>
+        <v>-4.383111909261392</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9903472613444668</v>
+        <v>1.065327350953261</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5275646673023836</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.584350186130424</v>
+        <v>-4.396899962108439</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9752687488375393</v>
+        <v>1.050248838446333</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5275646673023836</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.639870262023013</v>
+        <v>-4.452420038001028</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.090091555172706</v>
+        <v>1.1650716447815</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5275646673023836</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.464396002230544</v>
+        <v>-4.276945778208558</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.164848491081482</v>
+        <v>1.239828580690276</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5275646673023836</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.575332254871793</v>
+        <v>-4.387882030849807</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.096216018786189</v>
+        <v>1.171196108394983</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5275646673023836</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111297</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.54166870939951</v>
+        <v>-4.354218485377525</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.038219750376552</v>
+        <v>1.113199839985346</v>
       </c>
       <c r="F1941" t="n">
         <v>0.5612282127746655</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.481816090195787</v>
+        <v>-4.294365866173802</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.072333184490173</v>
+        <v>1.147313274098967</v>
       </c>
       <c r="F1942" t="n">
         <v>0.5612282127746655</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.395572627169409</v>
+        <v>-4.208122403147424</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.101776840274585</v>
+        <v>1.176756929883379</v>
       </c>
       <c r="F1943" t="n">
         <v>0.5612282127746655</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.440879446568389</v>
+        <v>-4.253429222546404</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.075429887959518</v>
+        <v>1.150409977568312</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5204180497654347</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.46991255127069</v>
+        <v>-4.282462327248705</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.064368519111699</v>
+        <v>1.139348608720494</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5204180497654347</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.377102069819831</v>
+        <v>-4.189651845797846</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.030765403583409</v>
+        <v>1.105745493192203</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6132285312162941</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.421491539149258</v>
+        <v>-4.234041315127273</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.014883091776239</v>
+        <v>1.089863181385033</v>
       </c>
       <c r="F1947" t="n">
         <v>0.5688390618868664</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.538033144254601</v>
+        <v>-4.350582920232616</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9633421582458248</v>
+        <v>1.038322247854619</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4522974567815236</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.425656143071928</v>
+        <v>-4.238205919049943</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.013784254549561</v>
+        <v>1.088764344158355</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4522974567815236</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.45343654097328</v>
+        <v>-4.265986316951295</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.014169297157559</v>
+        <v>1.089149386766353</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4245170588801706</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.571817213703419</v>
+        <v>-4.384366989681434</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8051727480661572</v>
+        <v>0.8801528376749512</v>
       </c>
       <c r="F1951" t="n">
         <v>0.3572992067291944</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.68043129214675</v>
+        <v>-4.492981068124765</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8818767774080303</v>
+        <v>0.9568568670168243</v>
       </c>
       <c r="F1952" t="n">
         <v>0.3572992067291944</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.645022253898607</v>
+        <v>-4.457572029876622</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9105534188096105</v>
+        <v>0.9855335084184045</v>
       </c>
       <c r="F1953" t="n">
         <v>0.3572992067291944</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.606638591340456</v>
+        <v>-4.419188367318471</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9233263251752395</v>
+        <v>0.9983064147840337</v>
       </c>
       <c r="F1954" t="n">
         <v>0.3956828692873455</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.42952226130529</v>
+        <v>-4.242072037283305</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9909018860346079</v>
+        <v>1.065881975643402</v>
       </c>
       <c r="F1955" t="n">
         <v>0.3956828692873455</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.474614506138836</v>
+        <v>-4.287164282116851</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9735483798631028</v>
+        <v>1.048528469471897</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3337868261179557</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.295239084900068</v>
+        <v>-4.107788860878083</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.039085523665024</v>
+        <v>1.114065613273818</v>
       </c>
       <c r="F1957" t="n">
         <v>0.4905635842886744</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.340253298420674</v>
+        <v>-4.152803074398689</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.001887293588372</v>
+        <v>1.076867383197166</v>
       </c>
       <c r="F1958" t="n">
         <v>0.4602146889740698</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.607257808693109</v>
+        <v>-4.419807584671124</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9007770518183433</v>
+        <v>0.9757571414271373</v>
       </c>
       <c r="F1959" t="n">
         <v>0.2658516509311212</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.708455590130281</v>
+        <v>-4.521005366108296</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8595018611399756</v>
+        <v>0.9344819507487698</v>
       </c>
       <c r="F1960" t="n">
         <v>0.197442837385802</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.70557166181546</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.701944623515969</v>
+        <v>-4.514494399493984</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8597062093400174</v>
+        <v>0.9346862989488116</v>
       </c>
       <c r="F1961" t="n">
         <v>0.197442837385802</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.682906495808671</v>
+        <v>-4.495456271786686</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8638461796311814</v>
+        <v>0.9388262692399754</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1392592260546075</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.71403312695929</v>
+        <v>-4.526582902937305</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9706899288051243</v>
+        <v>1.045670018413918</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1392592260546075</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.727899888293208</v>
+        <v>-4.540449664271223</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9659765532576907</v>
+        <v>1.040956642866485</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1014013093207846</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789119</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.683095716753278</v>
+        <v>-4.495645492731293</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9899067522705887</v>
+        <v>1.064886841879383</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1014013093207846</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.535352746518275</v>
+        <v>-4.34790252249629</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9469541616417891</v>
+        <v>1.021934251250583</v>
       </c>
       <c r="F1966" t="n">
         <v>0.2692086665556677</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.619173967792974</v>
+        <v>-4.431723743770989</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9162192946633907</v>
+        <v>0.9911993842721847</v>
       </c>
       <c r="F1967" t="n">
         <v>0.2692086665556677</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394725</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.613021261740189</v>
+        <v>-4.425571037718204</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9193427254761628</v>
+        <v>0.9943228150849568</v>
       </c>
       <c r="F1968" t="n">
         <v>0.275361372608452</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.629830559890691</v>
+        <v>-4.442380335868706</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9116994829560723</v>
+        <v>0.9866795725648663</v>
       </c>
       <c r="F1969" t="n">
         <v>0.2585520744579504</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798423</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.567532561114569</v>
+        <v>-4.380082337092584</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.002954236263342</v>
+        <v>1.077934325872136</v>
       </c>
       <c r="F1970" t="n">
         <v>0.2585520744579504</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.365742363449411</v>
+        <v>-4.178292139427426</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8859623170435325</v>
+        <v>0.9609424066523264</v>
       </c>
       <c r="F1971" t="n">
         <v>0.4565702666271048</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852427</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.416629076135606</v>
+        <v>-4.229178852113621</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9358978642912297</v>
+        <v>1.010877953900024</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4056835539409102</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.51436962076058</v>
+        <v>-4.326919396738595</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9114293825572837</v>
+        <v>0.9864094721660777</v>
       </c>
       <c r="F1973" t="n">
         <v>0.38979427580793</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.574578918765865</v>
+        <v>-4.38712869474388</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8858816441798414</v>
+        <v>0.9608617337886354</v>
       </c>
       <c r="F1974" t="n">
         <v>0.3295849778026455</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397789</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.498156872333938</v>
+        <v>-4.310706648311953</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9149420807925406</v>
+        <v>0.9899221704013346</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3295849778026455</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316244</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.45378374069537</v>
+        <v>-4.266333516673384</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9325542008834042</v>
+        <v>1.007534290492198</v>
       </c>
       <c r="F1976" t="n">
         <v>0.3739581094412141</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.476264091554254</v>
+        <v>-4.288813867532269</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9179558546784408</v>
+        <v>0.9929359442872348</v>
       </c>
       <c r="F1977" t="n">
         <v>0.3739581094412141</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.428608360993199</v>
+        <v>-4.241158136971213</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9433999039306677</v>
+        <v>1.018379993539462</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4216138400022698</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569613</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.328090202494444</v>
+        <v>-4.140639978472459</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9884995407048944</v>
+        <v>1.063479630313688</v>
       </c>
       <c r="F1979" t="n">
         <v>0.5221319985010243</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.388756792896833</v>
+        <v>-4.201306568874848</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9509875770198108</v>
+        <v>1.025967666628605</v>
       </c>
       <c r="F1980" t="n">
         <v>0.4404336817824906</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.343918391288435</v>
+        <v>-4.15646816726645</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9730206402737989</v>
+        <v>1.048000729882593</v>
       </c>
       <c r="F1981" t="n">
         <v>0.4449771147273601</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.363416847530443</v>
+        <v>-4.175966623508458</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9693821974080736</v>
+        <v>1.044362287016868</v>
       </c>
       <c r="F1982" t="n">
         <v>0.3968924734474558</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405954</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.319214010444543</v>
+        <v>-4.131763786422558</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.992942934770271</v>
+        <v>1.067923024379065</v>
       </c>
       <c r="F1983" t="n">
         <v>0.4410953105333563</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265639</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.356193038107985</v>
+        <v>-4.168742814086</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9765613241741413</v>
+        <v>1.051541413782935</v>
       </c>
       <c r="F1984" t="n">
         <v>0.4780692123246868</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284873</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.197901620568714</v>
+        <v>-4.010451396546729</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.09112565637289</v>
+        <v>1.166105745981684</v>
       </c>
       <c r="F1985" t="n">
         <v>0.4780692123246868</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321016</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.990259616934237</v>
+        <v>-3.802809392912252</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.172623162420933</v>
+        <v>1.247603252029727</v>
       </c>
       <c r="F1986" t="n">
         <v>0.685711215959163</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475133</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.939227524211709</v>
+        <v>-3.751777300189724</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.187984227748215</v>
+        <v>1.262964317357009</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7367433086816909</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404848</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.874003343084504</v>
+        <v>-3.686553119062519</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.231261304291802</v>
+        <v>1.306241393900596</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8019674898088965</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.83657632301337</v>
+        <v>-3.649126098991385</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.242193084619535</v>
+        <v>1.317173174228329</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8072190278380782</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.856687979048079</v>
+        <v>-3.669237755026094</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.235405214536893</v>
+        <v>1.310385304145687</v>
       </c>
       <c r="F1990" t="n">
         <v>0.8182463728354974</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82866144563628</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.802943164620874</v>
+        <v>-3.615492940598889</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.417460911328985</v>
+        <v>1.492441000937779</v>
       </c>
       <c r="F1991" t="n">
         <v>0.8283096822759594</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957619</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.728160903595861</v>
+        <v>-3.540710679573876</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.567486724956807</v>
+        <v>1.642466814565601</v>
       </c>
       <c r="F1992" t="n">
         <v>0.903091943300972</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998757</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.702076819332053</v>
+        <v>-3.514626595310068</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.56962833467619</v>
+        <v>1.644608424284984</v>
       </c>
       <c r="F1993" t="n">
         <v>0.903091943300972</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896923</v>
+        <v>3.80339781889693</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.623945638483106</v>
+        <v>-3.436495414461121</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.599074002599548</v>
+        <v>1.674054092208342</v>
       </c>
       <c r="F1994" t="n">
         <v>0.9772687541846565</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959851</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.615053177089823</v>
+        <v>-3.427602953067838</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.620185392883652</v>
+        <v>1.695165482492446</v>
       </c>
       <c r="F1995" t="n">
         <v>0.9772687541846565</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945359</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.783529294059701</v>
+        <v>-3.596079070037716</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.544649993500285</v>
+        <v>1.619630083109079</v>
       </c>
       <c r="F1996" t="n">
         <v>0.9493209184680758</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782701</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.085729765198118</v>
+        <v>-2.898279541176133</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.80503950223278</v>
+        <v>1.880019591841575</v>
       </c>
       <c r="F1997" t="n">
         <v>0.8789728590976651</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.78467134563263</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.063008661514965</v>
+        <v>-2.87555843749298</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.804791966202946</v>
+        <v>1.87977205581174</v>
       </c>
       <c r="F1998" t="n">
         <v>0.8789728590976651</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777667</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.192210474809008</v>
+        <v>-3.004760250787023</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.912017366736498</v>
+        <v>1.986997456345292</v>
       </c>
       <c r="F1999" t="n">
         <v>0.7497710458036229</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.346991481587263</v>
+        <v>-3.159541257565278</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.887182786518842</v>
+        <v>1.962162876127636</v>
       </c>
       <c r="F2000" t="n">
         <v>0.7164033717491467</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799959</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.33993679137209</v>
+        <v>-3.152486567350105</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.886680018594457</v>
+        <v>1.961660108203251</v>
       </c>
       <c r="F2001" t="n">
         <v>0.7234580619643205</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331111</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.312985567045602</v>
+        <v>-3.125535343023617</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.907466661969794</v>
+        <v>1.982446751578588</v>
       </c>
       <c r="F2002" t="n">
         <v>0.7383384079920396</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784109</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.448938575101918</v>
+        <v>-3.261488351079933</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.037188590892227</v>
+        <v>2.112168680501021</v>
       </c>
       <c r="F2003" t="n">
         <v>0.7383384079920396</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.47134669290679</v>
+        <v>-3.283896468884805</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.020342038673271</v>
+        <v>2.095322128282065</v>
       </c>
       <c r="F2004" t="n">
         <v>0.7383384079920396</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.61935246038619</v>
+        <v>-3.431902236364205</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.963193731231149</v>
+        <v>2.038173820839943</v>
       </c>
       <c r="F2005" t="n">
         <v>0.6516113991284982</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.62879338627472</v>
+        <v>-3.441343162252735</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.015671078597584</v>
+        <v>2.090651168206378</v>
       </c>
       <c r="F2006" t="n">
         <v>0.7740385166718896</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.681066993610361</v>
+        <v>-3.493616769588376</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.997652730208628</v>
+        <v>2.072632819817422</v>
       </c>
       <c r="F2007" t="n">
         <v>0.7217649093362484</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.757396971211267</v>
+        <v>-3.569946747189282</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.965232552062041</v>
+        <v>2.040212641670835</v>
       </c>
       <c r="F2008" t="n">
         <v>0.7217649093362484</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.95965069153562</v>
+        <v>-3.772200467513635</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.879151293535162</v>
+        <v>1.954131383143956</v>
       </c>
       <c r="F2009" t="n">
         <v>0.5195111890118949</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-4.121219117062875</v>
+        <v>-3.93376889304089</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.812957933534413</v>
+        <v>1.887938023143206</v>
       </c>
       <c r="F2010" t="n">
         <v>0.3927282652140155</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.7549119076471</v>
+        <v>3.754911907647106</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.253520409160428</v>
+        <v>-4.066070185138444</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.77311082356131</v>
+        <v>1.848090913170104</v>
       </c>
       <c r="F2011" t="n">
         <v>0.3927282652140155</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763529</v>
+        <v>3.749896851763534</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.255082051975288</v>
+        <v>-4.067631827953304</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.772486166435366</v>
+        <v>1.84746625604416</v>
       </c>
       <c r="F2012" t="n">
         <v>0.3927282652140155</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392112</v>
+        <v>3.715834055392118</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.28298283908476</v>
+        <v>-4.095532615062776</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.759849892718579</v>
+        <v>1.834829982327373</v>
       </c>
       <c r="F2013" t="n">
         <v>0.3581313410710807</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172523</v>
+        <v>3.684909939172528</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.405508941787654</v>
+        <v>-4.21805871776567</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.70760389561462</v>
+        <v>1.782583985223414</v>
       </c>
       <c r="F2014" t="n">
         <v>0.2356052383681868</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971074</v>
+        <v>3.61936224197108</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.636023437973243</v>
+        <v>-4.448573213951259</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.682104056730888</v>
+        <v>1.757084146339682</v>
       </c>
       <c r="F2015" t="n">
         <v>0.005090742182598085</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199802</v>
+        <v>3.640764248199807</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.892744255968067</v>
+        <v>-4.705294031946083</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.719727448534806</v>
+        <v>1.794707538143599</v>
       </c>
       <c r="F2016" t="n">
         <v>-0.1033238319612167</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622232</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-5.046730673744207</v>
+        <v>-4.859280449722224</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.727113150569989</v>
+        <v>1.802093240178783</v>
       </c>
       <c r="F2017" t="n">
         <v>-0.1033238319612167</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808524</v>
+        <v>3.61993717680853</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.996208769916541</v>
+        <v>-4.808758545894558</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.733373114221177</v>
+        <v>1.80835320382997</v>
       </c>
       <c r="F2018" t="n">
         <v>-0.1033238319612167</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.65634689399489</v>
+        <v>3.656346893994895</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.248683923924266</v>
+        <v>-5.061233699902282</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.644253541673501</v>
+        <v>1.719233631282294</v>
       </c>
       <c r="F2019" t="n">
         <v>-0.1033238319612167</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358294</v>
+        <v>3.674042696358299</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.518156725845974</v>
+        <v>-5.330706501823991</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.537674955423761</v>
+        <v>1.612655045032555</v>
       </c>
       <c r="F2020" t="n">
         <v>-0.1033238319612167</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637083</v>
+        <v>3.663523617637088</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.675700797575415</v>
+        <v>-5.488250573553432</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.478779068959306</v>
+        <v>1.553759158568099</v>
       </c>
       <c r="F2021" t="n">
         <v>-0.1702256371014912</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301339</v>
+        <v>3.652163313301344</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.953665193158689</v>
+        <v>-5.766214969136706</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.362671163462186</v>
+        <v>1.43765125307098</v>
       </c>
       <c r="F2022" t="n">
         <v>-0.2598453713869755</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215465</v>
+        <v>3.667976467215471</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-6.07063288579758</v>
+        <v>-5.883182661775597</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.478088143105674</v>
+        <v>1.553068232714467</v>
       </c>
       <c r="F2023" t="n">
         <v>-0.2598453713869755</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456688</v>
+        <v>3.696553628456693</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.155350828018533</v>
+        <v>-5.96790060399655</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.439047604181107</v>
+        <v>1.5140276937899</v>
       </c>
       <c r="F2024" t="n">
         <v>-0.3449614003150219</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253283</v>
+        <v>3.750058176253289</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.237285646287416</v>
+        <v>-6.049835422265433</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.416503094442044</v>
+        <v>1.491483184050838</v>
       </c>
       <c r="F2025" t="n">
         <v>-0.3548961459021021</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717827</v>
+        <v>3.783647027717833</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.183547472887154</v>
+        <v>-5.996097248865171</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.446924002258052</v>
+        <v>1.521904091866845</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.30115797250184</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616945</v>
+        <v>3.79831094461695</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.073541189409933</v>
+        <v>-5.886090965387949</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.483079402893116</v>
+        <v>1.55805949250191</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.2779534005845647</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203659</v>
+        <v>3.785578085203665</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.930481613669008</v>
+        <v>-5.743031389647024</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.54455324391146</v>
+        <v>1.619533333520254</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.2699399739945855</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436925</v>
+        <v>3.77725157243693</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.62903488819717</v>
+        <v>-5.441584664175187</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.672392816982732</v>
+        <v>1.747372906591525</v>
       </c>
       <c r="F2029" t="n">
         <v>0.03150675147725179</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064763</v>
+        <v>3.812650101064769</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.653625132432354</v>
+        <v>-5.466174908410371</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.663527897041368</v>
+        <v>1.738507986650161</v>
       </c>
       <c r="F2030" t="n">
         <v>0.03150675147725179</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859297</v>
+        <v>3.821198342859303</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.602586756425834</v>
+        <v>-5.41513653240385</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.684786151823732</v>
+        <v>1.759766241432525</v>
       </c>
       <c r="F2031" t="n">
         <v>0.03150675147725179</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354682</v>
+        <v>3.831748677354687</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.561447461559203</v>
+        <v>-5.373997237537219</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.72027996864453</v>
+        <v>1.795260058253323</v>
       </c>
       <c r="F2032" t="n">
         <v>0.07264604634388261</v>
@@ -48304,16 +48304,16 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085616</v>
+        <v>3.825767093085622</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.450841321479601</v>
+        <v>-5.263391097457617</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.580706420800305</v>
+        <v>1.655686510409098</v>
       </c>
       <c r="F2033" t="n">
         <v>0.1832521864234846</v>
@@ -48327,16 +48327,16 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462778</v>
+        <v>3.804703121462784</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.581422056010443</v>
+        <v>-5.39397183198846</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.531976171061932</v>
+        <v>1.606956260670725</v>
       </c>
       <c r="F2034" t="n">
         <v>0.05267145189264211</v>
@@ -48350,16 +48350,16 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218596</v>
+        <v>3.775043021218601</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.416925721819482</v>
+        <v>-5.229475497797498</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.582201523814399</v>
+        <v>1.657181613423192</v>
       </c>
       <c r="F2035" t="n">
         <v>0.05267145189264211</v>
@@ -48373,16 +48373,16 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462767</v>
+        <v>3.821044820462772</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.29244524109553</v>
+        <v>-5.104995017073547</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.631181426540409</v>
+        <v>1.706161516149202</v>
       </c>
       <c r="F2036" t="n">
         <v>0.05267145189264211</v>
@@ -48396,16 +48396,16 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533049</v>
+        <v>3.832321184533054</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.302830435985419</v>
+        <v>-5.115380211963436</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.636896127709526</v>
+        <v>1.711876217318319</v>
       </c>
       <c r="F2037" t="n">
         <v>0.04228625700275279</v>
@@ -48419,16 +48419,16 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.527515540589915</v>
+        <v>3.820905064379637</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.212075959956778</v>
+        <v>-5.024625735934794</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.744034923897408</v>
+        <v>1.819015013506201</v>
       </c>
       <c r="F2038" t="n">
         <v>0.1330407330313945</v>

--- a/tame_output/ON/bt/strategyON_20240728.xlsx
+++ b/tame_output/ON/bt/strategyON_20240728.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-80.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.2%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.9%</t>
+          <t>454.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-664.0%</t>
+          <t>-689.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24649.4%</t>
+          <t>-24645.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-194.3%</t>
+          <t>-204.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-210.7%</t>
+          <t>-209.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-55.1%</t>
+          <t>-70.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2038"/>
+  <dimension ref="A1:G2039"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.835835482065201</v>
+        <v>-8.090151573221696</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.01642573307558548</v>
+        <v>-0.08530070338701279</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.314228376767125</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.79565118369901</v>
+        <v>-8.049967274855506</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.03284307630990302</v>
+        <v>-0.06888336015269525</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.274044078400934</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.632251312759648</v>
+        <v>-7.886567403916144</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.09756984590640494</v>
+        <v>-0.004156590556193329</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.110644207461571</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.398770090530049</v>
+        <v>-7.653086181686545</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1988867636360969</v>
+        <v>0.09716032717349865</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.8771629852319727</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785789</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.249103699522534</v>
+        <v>-7.50341979067903</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2558611097261436</v>
+        <v>0.1541346732635454</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7842594939894367</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.116828225891648</v>
+        <v>-7.371144317048143</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3041387859255251</v>
+        <v>0.2024123494629269</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.6519840203585501</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.961089893331906</v>
+        <v>-7.215405984488402</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3692491796370589</v>
+        <v>0.2675227431744602</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4962456877988085</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.712090094648325</v>
+        <v>-6.966406185804821</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4817554403341497</v>
+        <v>0.3800290038715515</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2472458891152278</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.817680084421429</v>
+        <v>-7.071996175577925</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3115435148256895</v>
+        <v>0.2098170783630913</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3528358788883322</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.836414986540026</v>
+        <v>-7.090731077696522</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3525938958553372</v>
+        <v>0.2508674593927385</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3584318885484635</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.688474945132427</v>
+        <v>-6.942791036288923</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2918909897302093</v>
+        <v>0.1901645532676106</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.3381109726399059</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.635505422878438</v>
+        <v>-6.889821514034934</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3043648123783265</v>
+        <v>0.2026383759157282</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.285141450385917</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.591957016107748</v>
+        <v>-6.846273107264244</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3148235629915095</v>
+        <v>0.2130971265289112</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.285141450385917</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.558593809628979</v>
+        <v>-6.812909900785475</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3426311999641598</v>
+        <v>0.2409047635015615</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.285141450385917</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.450334672506457</v>
+        <v>-6.704650763662953</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3804669752723635</v>
+        <v>0.2787405388097652</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.285141450385917</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.327043537689327</v>
+        <v>-6.581359628845822</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4272815232097931</v>
+        <v>0.3255550867471944</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.1618503155687865</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.305894338785883</v>
+        <v>-6.560210429942379</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4434421810084954</v>
+        <v>0.3417157445458971</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.1407011166653432</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.062128896802439</v>
+        <v>-6.316444987958935</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5367290661489239</v>
+        <v>0.4350026296863256</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.1407011166653432</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.960366076525144</v>
+        <v>-6.21468216768164</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5795585081798578</v>
+        <v>0.4778320717172595</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.1274820482729145</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.710515682576069</v>
+        <v>-5.964831773732565</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6722407407431898</v>
+        <v>0.5705143042805916</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.1274820482729145</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.534623590108637</v>
+        <v>-5.788939681265132</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7461967012508115</v>
+        <v>0.6444702647882132</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.1274820482729145</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.363177127086174</v>
+        <v>-5.617493218242669</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8281027925143505</v>
+        <v>0.7263763560517527</v>
       </c>
       <c r="F1921" t="n">
         <v>0.04396441474954865</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.288887561347835</v>
+        <v>-5.54320365250433</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8568390964259831</v>
+        <v>0.7551126599633853</v>
       </c>
       <c r="F1922" t="n">
         <v>0.1182539804878879</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.2252518191139</v>
+        <v>-5.479567910270395</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.886988194373874</v>
+        <v>0.7852617579112762</v>
       </c>
       <c r="F1923" t="n">
         <v>0.1818897227218225</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.11382505978798</v>
+        <v>-5.368141150944475</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.912753156888038</v>
+        <v>0.8110267204254398</v>
       </c>
       <c r="F1924" t="n">
         <v>0.1818897227218225</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.124327682853269</v>
+        <v>-5.378643774009764</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9102951842867997</v>
+        <v>0.8085687478242018</v>
       </c>
       <c r="F1925" t="n">
         <v>0.1713870996565336</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.052085114682074</v>
+        <v>-5.306401205838569</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9431215253900977</v>
+        <v>0.8413950889274999</v>
       </c>
       <c r="F1926" t="n">
         <v>0.1713870996565336</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.034371427804209</v>
+        <v>-5.288687518960704</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9508855840585837</v>
+        <v>0.8491591475959859</v>
       </c>
       <c r="F1927" t="n">
         <v>0.1745684285534504</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.989951135593245</v>
+        <v>-5.251427831567751</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9656517721629632</v>
+        <v>0.8610610937731606</v>
       </c>
       <c r="F1928" t="n">
         <v>0.1745684285534504</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.769930337556234</v>
+        <v>-5.031407033530741</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.055239128388382</v>
+        <v>0.950648449998579</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3157882736214306</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.637062648492956</v>
+        <v>-4.898539344467463</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.124280386815516</v>
+        <v>1.019689708425713</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3157882736214306</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.516889565128458</v>
+        <v>-4.778366261102964</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.173495464601617</v>
+        <v>1.068904786211815</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4359613569859296</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.37221742002872</v>
+        <v>-4.633694116003227</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.241452425202952</v>
+        <v>1.136861746813149</v>
       </c>
       <c r="F1932" t="n">
         <v>0.580633502085667</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942105</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.432092247386413</v>
+        <v>-4.693568943360919</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.203539985661301</v>
+        <v>1.098949307271498</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5207586747279749</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.312272016475576</v>
+        <v>-4.573748712450082</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.266757247259844</v>
+        <v>1.162166568870042</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5207586747279749</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.314741722937382</v>
+        <v>-4.576218418911888</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.173413563997563</v>
+        <v>1.068822885607761</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5182889682661687</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.383111909261392</v>
+        <v>-4.644588605235898</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.065327350953261</v>
+        <v>0.9607366725634581</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5275646673023836</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.396899962108439</v>
+        <v>-4.658376658082945</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.050248838446333</v>
+        <v>0.9456581600565308</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5275646673023836</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.452420038001028</v>
+        <v>-4.713896733975535</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.1650716447815</v>
+        <v>1.060480966391697</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5275646673023836</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.276945778208558</v>
+        <v>-4.538422474183065</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.239828580690276</v>
+        <v>1.135237902300473</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5275646673023836</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.387882030849807</v>
+        <v>-4.649358726824314</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.171196108394983</v>
+        <v>1.06660543000518</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5275646673023836</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111297</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.354218485377525</v>
+        <v>-4.615695181352032</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.113199839985346</v>
+        <v>1.008609161595543</v>
       </c>
       <c r="F1941" t="n">
         <v>0.5612282127746655</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.294365866173802</v>
+        <v>-4.555842562148309</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.147313274098967</v>
+        <v>1.042722595709165</v>
       </c>
       <c r="F1942" t="n">
         <v>0.5612282127746655</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.208122403147424</v>
+        <v>-4.469599099121931</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.176756929883379</v>
+        <v>1.072166251493576</v>
       </c>
       <c r="F1943" t="n">
         <v>0.5612282127746655</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.253429222546404</v>
+        <v>-4.514905918520911</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.150409977568312</v>
+        <v>1.04581929917851</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5204180497654347</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.282462327248705</v>
+        <v>-4.543939023223212</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.139348608720494</v>
+        <v>1.034757930330691</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5204180497654347</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.189651845797846</v>
+        <v>-4.451128541772352</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.105745493192203</v>
+        <v>1.0011548148024</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6132285312162941</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.234041315127273</v>
+        <v>-4.49551801110178</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.089863181385033</v>
+        <v>0.9852725029952303</v>
       </c>
       <c r="F1947" t="n">
         <v>0.5688390618868664</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.350582920232616</v>
+        <v>-4.612059616207122</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.038322247854619</v>
+        <v>0.9337315694648163</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4522974567815236</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.238205919049943</v>
+        <v>-4.499682615024449</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.088764344158355</v>
+        <v>0.9841736657685527</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4522974567815236</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.265986316951295</v>
+        <v>-4.527463012925802</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.089149386766353</v>
+        <v>0.9845587083765506</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4245170588801706</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.384366989681434</v>
+        <v>-4.64584368565594</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8801528376749512</v>
+        <v>0.7755621592851485</v>
       </c>
       <c r="F1951" t="n">
         <v>0.3572992067291944</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.492981068124765</v>
+        <v>-4.754457764099271</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9568568670168243</v>
+        <v>0.8522661886270217</v>
       </c>
       <c r="F1952" t="n">
         <v>0.3572992067291944</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.457572029876622</v>
+        <v>-4.719048725851128</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9855335084184045</v>
+        <v>0.880942830028602</v>
       </c>
       <c r="F1953" t="n">
         <v>0.3572992067291944</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.419188367318471</v>
+        <v>-4.680665063292977</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9983064147840337</v>
+        <v>0.893715736394231</v>
       </c>
       <c r="F1954" t="n">
         <v>0.3956828692873455</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.242072037283305</v>
+        <v>-4.503548733257811</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.065881975643402</v>
+        <v>0.9612912972535994</v>
       </c>
       <c r="F1955" t="n">
         <v>0.3956828692873455</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.287164282116851</v>
+        <v>-4.548640978091357</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.048528469471897</v>
+        <v>0.9439377910820941</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3337868261179557</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.107788860878083</v>
+        <v>-4.369265556852589</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.114065613273818</v>
+        <v>1.009474934884016</v>
       </c>
       <c r="F1957" t="n">
         <v>0.4905635842886744</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.152803074398689</v>
+        <v>-4.414279770373195</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.076867383197166</v>
+        <v>0.9722767048073631</v>
       </c>
       <c r="F1958" t="n">
         <v>0.4602146889740698</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.419807584671124</v>
+        <v>-4.68128428064563</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9757571414271373</v>
+        <v>0.8711664630373348</v>
       </c>
       <c r="F1959" t="n">
         <v>0.2658516509311212</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760815</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.521005366108296</v>
+        <v>-4.782482062082803</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9344819507487698</v>
+        <v>0.8298912723589671</v>
       </c>
       <c r="F1960" t="n">
         <v>0.197442837385802</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70557166181546</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.514494399493984</v>
+        <v>-4.77597109546849</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9346862989488116</v>
+        <v>0.8300956205590089</v>
       </c>
       <c r="F1961" t="n">
         <v>0.197442837385802</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.495456271786686</v>
+        <v>-4.756932967761193</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9388262692399754</v>
+        <v>0.8342355908501728</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1392592260546075</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.526582902937305</v>
+        <v>-4.788059598911811</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.045670018413918</v>
+        <v>0.9410793400241158</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1392592260546075</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.540449664271223</v>
+        <v>-4.801926360245729</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.040956642866485</v>
+        <v>0.9363659644766822</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1014013093207846</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789119</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.495645492731293</v>
+        <v>-4.757122188705799</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.064886841879383</v>
+        <v>0.9602961634895801</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1014013093207846</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.34790252249629</v>
+        <v>-4.609379218470797</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.021934251250583</v>
+        <v>0.9173435728607806</v>
       </c>
       <c r="F1966" t="n">
         <v>0.2692086665556677</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.431723743770989</v>
+        <v>-4.693200439745495</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9911993842721847</v>
+        <v>0.8866087058823822</v>
       </c>
       <c r="F1967" t="n">
         <v>0.2692086665556677</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.425571037718204</v>
+        <v>-4.687047733692711</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9943228150849568</v>
+        <v>0.8897321366951543</v>
       </c>
       <c r="F1968" t="n">
         <v>0.275361372608452</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.442380335868706</v>
+        <v>-4.703857031843213</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9866795725648663</v>
+        <v>0.8820888941750638</v>
       </c>
       <c r="F1969" t="n">
         <v>0.2585520744579504</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.380082337092584</v>
+        <v>-4.64155903306709</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.077934325872136</v>
+        <v>0.9733436474823336</v>
       </c>
       <c r="F1970" t="n">
         <v>0.2585520744579504</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.178292139427426</v>
+        <v>-4.439768835401932</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9609424066523264</v>
+        <v>0.8563517282625237</v>
       </c>
       <c r="F1971" t="n">
         <v>0.4565702666271048</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852427</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.229178852113621</v>
+        <v>-4.490655548088127</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.010877953900024</v>
+        <v>0.9062872755102211</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4056835539409102</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.326919396738595</v>
+        <v>-4.588396092713102</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9864094721660777</v>
+        <v>0.8818187937762749</v>
       </c>
       <c r="F1973" t="n">
         <v>0.38979427580793</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.38712869474388</v>
+        <v>-4.648605390718386</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9608617337886354</v>
+        <v>0.8562710553988326</v>
       </c>
       <c r="F1974" t="n">
         <v>0.3295849778026455</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.310706648311953</v>
+        <v>-4.57218334428646</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9899221704013346</v>
+        <v>0.8853314920115321</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3295849778026455</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.266333516673384</v>
+        <v>-4.527810212647891</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.007534290492198</v>
+        <v>0.9029436121023957</v>
       </c>
       <c r="F1976" t="n">
         <v>0.3739581094412141</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.288813867532269</v>
+        <v>-4.550290563506776</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9929359442872348</v>
+        <v>0.8883452658974322</v>
       </c>
       <c r="F1977" t="n">
         <v>0.3739581094412141</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.241158136971213</v>
+        <v>-4.50263483294572</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.018379993539462</v>
+        <v>0.9137893151496592</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4216138400022698</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.140639978472459</v>
+        <v>-4.402116674446965</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.063479630313688</v>
+        <v>0.9588889519238859</v>
       </c>
       <c r="F1979" t="n">
         <v>0.5221319985010243</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.201306568874848</v>
+        <v>-4.462783264849355</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.025967666628605</v>
+        <v>0.9213769882388023</v>
       </c>
       <c r="F1980" t="n">
         <v>0.4404336817824906</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.15646816726645</v>
+        <v>-4.417944863240956</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.048000729882593</v>
+        <v>0.9434100514927903</v>
       </c>
       <c r="F1981" t="n">
         <v>0.4449771147273601</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.175966623508458</v>
+        <v>-4.437443319482965</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.044362287016868</v>
+        <v>0.9397716086270651</v>
       </c>
       <c r="F1982" t="n">
         <v>0.3968924734474558</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.131763786422558</v>
+        <v>-4.393240482397064</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.067923024379065</v>
+        <v>0.9633323459892624</v>
       </c>
       <c r="F1983" t="n">
         <v>0.4410953105333563</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.168742814086</v>
+        <v>-4.430219510060507</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.051541413782935</v>
+        <v>0.9469507353931328</v>
       </c>
       <c r="F1984" t="n">
         <v>0.4780692123246868</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.010451396546729</v>
+        <v>-4.271928092521235</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.166105745981684</v>
+        <v>1.061515067591881</v>
       </c>
       <c r="F1985" t="n">
         <v>0.4780692123246868</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321018</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.802809392912252</v>
+        <v>-4.064286088886758</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.247603252029727</v>
+        <v>1.143012573639925</v>
       </c>
       <c r="F1986" t="n">
         <v>0.685711215959163</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.751777300189724</v>
+        <v>-4.013253996164231</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.262964317357009</v>
+        <v>1.158373638967206</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7367433086816909</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404853</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.686553119062519</v>
+        <v>-3.948029815037025</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.306241393900596</v>
+        <v>1.201650715510793</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8019674898088965</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.649126098991385</v>
+        <v>-3.910602794965892</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.317173174228329</v>
+        <v>1.212582495838527</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8072190278380782</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.669237755026094</v>
+        <v>-3.9307144510006</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.310385304145687</v>
+        <v>1.205794625755884</v>
       </c>
       <c r="F1990" t="n">
         <v>0.8182463728354974</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.615492940598889</v>
+        <v>-3.876969636573395</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.492441000937779</v>
+        <v>1.387850322547977</v>
       </c>
       <c r="F1991" t="n">
         <v>0.8283096822759594</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.540710679573876</v>
+        <v>-3.802187375548383</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.642466814565601</v>
+        <v>1.537876136175799</v>
       </c>
       <c r="F1992" t="n">
         <v>0.903091943300972</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998757</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.514626595310068</v>
+        <v>-3.776103291284575</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.644608424284984</v>
+        <v>1.540017745895181</v>
       </c>
       <c r="F1993" t="n">
         <v>0.903091943300972</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.80339781889693</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.436495414461121</v>
+        <v>-3.697972110435628</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.674054092208342</v>
+        <v>1.569463413818539</v>
       </c>
       <c r="F1994" t="n">
         <v>0.9772687541846565</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959853</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.427602953067838</v>
+        <v>-3.689079649042345</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.695165482492446</v>
+        <v>1.590574804102644</v>
       </c>
       <c r="F1995" t="n">
         <v>0.9772687541846565</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.596079070037716</v>
+        <v>-3.857555766012223</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.619630083109079</v>
+        <v>1.515039404719277</v>
       </c>
       <c r="F1996" t="n">
         <v>0.9493209184680758</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782703</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.898279541176133</v>
+        <v>-3.159756237150639</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.880019591841575</v>
+        <v>1.775428913451772</v>
       </c>
       <c r="F1997" t="n">
         <v>0.8789728590976651</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632632</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.87555843749298</v>
+        <v>-3.137035133467487</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.87977205581174</v>
+        <v>1.775181377421937</v>
       </c>
       <c r="F1998" t="n">
         <v>0.8789728590976651</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.004760250787023</v>
+        <v>-3.266236946761529</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.986997456345292</v>
+        <v>1.882406777955489</v>
       </c>
       <c r="F1999" t="n">
         <v>0.7497710458036229</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.159541257565278</v>
+        <v>-3.421017953539785</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.962162876127636</v>
+        <v>1.857572197737834</v>
       </c>
       <c r="F2000" t="n">
         <v>0.7164033717491467</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.152486567350105</v>
+        <v>-3.413963263324611</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.961660108203251</v>
+        <v>1.857069429813448</v>
       </c>
       <c r="F2001" t="n">
         <v>0.7234580619643205</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.125535343023617</v>
+        <v>-3.387012038998123</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.982446751578588</v>
+        <v>1.877856073188785</v>
       </c>
       <c r="F2002" t="n">
         <v>0.7383384079920396</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784109</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.261488351079933</v>
+        <v>-3.52296504705444</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.112168680501021</v>
+        <v>2.007578002111218</v>
       </c>
       <c r="F2003" t="n">
         <v>0.7383384079920396</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.283896468884805</v>
+        <v>-3.545373164859312</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.095322128282065</v>
+        <v>1.990731449892262</v>
       </c>
       <c r="F2004" t="n">
         <v>0.7383384079920396</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.431902236364205</v>
+        <v>-3.693378932338711</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.038173820839943</v>
+        <v>1.93358314245014</v>
       </c>
       <c r="F2005" t="n">
         <v>0.6516113991284982</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.441343162252735</v>
+        <v>-3.702819858227241</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.090651168206378</v>
+        <v>1.986060489816575</v>
       </c>
       <c r="F2006" t="n">
         <v>0.7740385166718896</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.493616769588376</v>
+        <v>-3.755093465562882</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.072632819817422</v>
+        <v>1.968042141427619</v>
       </c>
       <c r="F2007" t="n">
         <v>0.7217649093362484</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.569946747189282</v>
+        <v>-3.831423443163788</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.040212641670835</v>
+        <v>1.935621963281033</v>
       </c>
       <c r="F2008" t="n">
         <v>0.7217649093362484</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.772200467513635</v>
+        <v>-4.033677163488142</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.954131383143956</v>
+        <v>1.849540704754153</v>
       </c>
       <c r="F2009" t="n">
         <v>0.5195111890118949</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.93376889304089</v>
+        <v>-4.195245589015397</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.887938023143206</v>
+        <v>1.783347344753404</v>
       </c>
       <c r="F2010" t="n">
         <v>0.3927282652140155</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647106</v>
+        <v>3.754911907647102</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.066070185138444</v>
+        <v>-4.32754688111295</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.848090913170104</v>
+        <v>1.743500234780301</v>
       </c>
       <c r="F2011" t="n">
         <v>0.3927282652140155</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763534</v>
+        <v>3.749896851763529</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.067631827953304</v>
+        <v>-4.32910852392781</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.84746625604416</v>
+        <v>1.742875577654357</v>
       </c>
       <c r="F2012" t="n">
         <v>0.3927282652140155</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392118</v>
+        <v>3.715834055392112</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.095532615062776</v>
+        <v>-4.357009311037283</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.834829982327373</v>
+        <v>1.73023930393757</v>
       </c>
       <c r="F2013" t="n">
         <v>0.3581313410710807</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172528</v>
+        <v>3.684909939172523</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.21805871776567</v>
+        <v>-4.479535413740177</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.782583985223414</v>
+        <v>1.677993306833611</v>
       </c>
       <c r="F2014" t="n">
         <v>0.2356052383681868</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.61936224197108</v>
+        <v>3.619362241971074</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.448573213951259</v>
+        <v>-4.710049909925766</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.757084146339682</v>
+        <v>1.65249346794988</v>
       </c>
       <c r="F2015" t="n">
         <v>0.005090742182598085</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199807</v>
+        <v>3.640764248199802</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.705294031946083</v>
+        <v>-4.96677072792059</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.794707538143599</v>
+        <v>1.690116859753797</v>
       </c>
       <c r="F2016" t="n">
         <v>-0.1033238319612167</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622232</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.859280449722224</v>
+        <v>-5.12075714569673</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.802093240178783</v>
+        <v>1.69750256178898</v>
       </c>
       <c r="F2017" t="n">
         <v>-0.1033238319612167</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61993717680853</v>
+        <v>3.619937176808524</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.808758545894558</v>
+        <v>-5.070235241869065</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.80835320382997</v>
+        <v>1.703762525440168</v>
       </c>
       <c r="F2018" t="n">
         <v>-0.1033238319612167</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994895</v>
+        <v>3.65634689399489</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.061233699902282</v>
+        <v>-5.322710395876789</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.719233631282294</v>
+        <v>1.614642952892492</v>
       </c>
       <c r="F2019" t="n">
         <v>-0.1033238319612167</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358299</v>
+        <v>3.674042696358294</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.330706501823991</v>
+        <v>-5.592183197798497</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.612655045032555</v>
+        <v>1.508064366642752</v>
       </c>
       <c r="F2020" t="n">
         <v>-0.1033238319612167</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637088</v>
+        <v>3.663523617637083</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.488250573553432</v>
+        <v>-5.749727269527939</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.553759158568099</v>
+        <v>1.449168480178297</v>
       </c>
       <c r="F2021" t="n">
         <v>-0.1702256371014912</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301344</v>
+        <v>3.65216331330134</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.766214969136706</v>
+        <v>-6.027691665111212</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.43765125307098</v>
+        <v>1.333060574681177</v>
       </c>
       <c r="F2022" t="n">
         <v>-0.2598453713869755</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215471</v>
+        <v>3.667976467215466</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.883182661775597</v>
+        <v>-6.144659357750103</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.553068232714467</v>
+        <v>1.448477554324665</v>
       </c>
       <c r="F2023" t="n">
         <v>-0.2598453713869755</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456693</v>
+        <v>3.696553628456688</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.96790060399655</v>
+        <v>-6.229377299971056</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.5140276937899</v>
+        <v>1.409437015400098</v>
       </c>
       <c r="F2024" t="n">
         <v>-0.3449614003150219</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253289</v>
+        <v>3.750058176253284</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.049835422265433</v>
+        <v>-6.31131211823994</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.491483184050838</v>
+        <v>1.386892505661035</v>
       </c>
       <c r="F2025" t="n">
         <v>-0.3548961459021021</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717833</v>
+        <v>3.783647027717828</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.996097248865171</v>
+        <v>-6.257573944839677</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.521904091866845</v>
+        <v>1.417313413477043</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.30115797250184</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.79831094461695</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.886090965387949</v>
+        <v>-6.147567661362456</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.55805949250191</v>
+        <v>1.453468814112107</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.2779534005845647</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203665</v>
+        <v>3.785578085203659</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.743031389647024</v>
+        <v>-6.004508085621531</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.619533333520254</v>
+        <v>1.514942655130451</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.2699399739945855</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77725157243693</v>
+        <v>3.777251572436925</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.441584664175187</v>
+        <v>-5.703061360149693</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.747372906591525</v>
+        <v>1.642782228201722</v>
       </c>
       <c r="F2029" t="n">
         <v>0.03150675147725179</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064769</v>
+        <v>3.812650101064763</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.466174908410371</v>
+        <v>-5.727651604384877</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.738507986650161</v>
+        <v>1.633917308260359</v>
       </c>
       <c r="F2030" t="n">
         <v>0.03150675147725179</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859303</v>
+        <v>3.821198342859297</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.41513653240385</v>
+        <v>-5.676613228378357</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.759766241432525</v>
+        <v>1.655175563042723</v>
       </c>
       <c r="F2031" t="n">
         <v>0.03150675147725179</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354687</v>
+        <v>3.831748677354682</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.373997237537219</v>
+        <v>-5.635473933511726</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.795260058253323</v>
+        <v>1.69066937986352</v>
       </c>
       <c r="F2032" t="n">
         <v>0.07264604634388261</v>
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085622</v>
+        <v>3.825767093085617</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.263391097457617</v>
+        <v>-5.625924540268749</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.655686510409098</v>
+        <v>1.510673133284645</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1832521864234846</v>
+        <v>0.08219543958685932</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.871350685559984</v>
+        <v>3.810716637458008</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462784</v>
+        <v>3.804703121462779</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.39397183198846</v>
+        <v>-5.756505274799592</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.606956260670725</v>
+        <v>1.461942883546272</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.05267145189264211</v>
+        <v>-0.04838529494398319</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.796504288915441</v>
+        <v>3.735870240813466</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218601</v>
+        <v>3.775043021218597</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.229475497797498</v>
+        <v>-5.59200894060863</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.657181613423192</v>
+        <v>1.512168236298739</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.05267145189264211</v>
+        <v>-0.04838529494398319</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.780931107991524</v>
+        <v>3.720297059889549</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462772</v>
+        <v>3.821044820462766</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.104995017073547</v>
+        <v>-5.467528459884679</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.706161516149202</v>
+        <v>1.56114813902475</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.05267145189264211</v>
+        <v>-0.04838529494398319</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.780118818427954</v>
+        <v>3.719484770325979</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533054</v>
+        <v>3.832321184533047</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.115380211963436</v>
+        <v>-5.477913654774568</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.711876217318319</v>
+        <v>1.566862840193866</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.04228625700275279</v>
+        <v>-0.05877048983387251</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.783756480619093</v>
+        <v>3.723122432517118</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,45 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.820905064379637</v>
+        <v>3.834429654120417</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.024625735934794</v>
+        <v>-5.273910583891343</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.819015013506201</v>
+        <v>1.719301074323581</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1330407330313945</v>
+        <v>0.1452325810493524</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.909046172012703</v>
+        <v>3.916361280823478</v>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" s="2" t="n">
+        <v>45501</v>
+      </c>
+      <c r="B2039" t="n">
+        <v>3.820933520566775</v>
+      </c>
+      <c r="C2039" t="n">
+        <v>3.759680923721239</v>
+      </c>
+      <c r="D2039" t="n">
+        <v>-5.273910583891343</v>
+      </c>
+      <c r="E2039" t="n">
+        <v>1.719301074323581</v>
+      </c>
+      <c r="F2039" t="n">
+        <v>0.1452325810493524</v>
+      </c>
+      <c r="G2039" t="n">
+        <v>3.752744720707607</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240728.xlsx
+++ b/tame_output/ON/bt/strategyON_20240728.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>72.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>111.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.8%</t>
+          <t>126.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.6%</t>
+          <t>454.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-689.0%</t>
+          <t>-664.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24645.4%</t>
+          <t>-24648.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-204.3%</t>
+          <t>-194.4%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-122.5%</t>
+          <t>-116.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-209.5%</t>
+          <t>-210.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-63.0%</t>
         </is>
       </c>
     </row>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.090151573221696</v>
+        <v>-7.835835482065201</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.08530070338701279</v>
+        <v>0.01642573307558548</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.314228376767125</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.049967274855506</v>
+        <v>-7.79565118369901</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.06888336015269525</v>
+        <v>0.03284307630990302</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.274044078400934</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.886567403916144</v>
+        <v>-7.632251312759648</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.004156590556193329</v>
+        <v>0.09756984590640494</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.110644207461571</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.653086181686545</v>
+        <v>-7.398770090530049</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.09716032717349865</v>
+        <v>0.1988867636360969</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.8771629852319727</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.50341979067903</v>
+        <v>-7.249103699522534</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.1541346732635454</v>
+        <v>0.2558611097261436</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7842594939894367</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.371144317048143</v>
+        <v>-7.116828225891648</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2024123494629269</v>
+        <v>0.3041387859255251</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.6519840203585501</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.215405984488402</v>
+        <v>-6.961089893331906</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2675227431744602</v>
+        <v>0.3692491796370589</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4962456877988085</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.966406185804821</v>
+        <v>-6.712090094648325</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3800290038715515</v>
+        <v>0.4817554403341497</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2472458891152278</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.071996175577925</v>
+        <v>-6.817680084421429</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2098170783630913</v>
+        <v>0.3115435148256895</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3528358788883322</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.090731077696522</v>
+        <v>-6.836414986540026</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2508674593927385</v>
+        <v>0.3525938958553372</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3584318885484635</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.942791036288923</v>
+        <v>-6.688474945132427</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1901645532676106</v>
+        <v>0.2918909897302093</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.3381109726399059</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.889821514034934</v>
+        <v>-6.635505422878438</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2026383759157282</v>
+        <v>0.3043648123783265</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.285141450385917</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.846273107264244</v>
+        <v>-6.591957016107748</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2130971265289112</v>
+        <v>0.3148235629915095</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.285141450385917</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.812909900785475</v>
+        <v>-6.558593809628979</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2409047635015615</v>
+        <v>0.3426311999641598</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.285141450385917</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.704650763662953</v>
+        <v>-6.450334672506457</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2787405388097652</v>
+        <v>0.3804669752723635</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.285141450385917</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.581359628845822</v>
+        <v>-6.327043537689327</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3255550867471944</v>
+        <v>0.4272815232097931</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.1618503155687865</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.560210429942379</v>
+        <v>-6.305894338785883</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3417157445458971</v>
+        <v>0.4434421810084954</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.1407011166653432</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.316444987958935</v>
+        <v>-6.062128896802439</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4350026296863256</v>
+        <v>0.5367290661489239</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.1407011166653432</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.21468216768164</v>
+        <v>-5.960366076525144</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4778320717172595</v>
+        <v>0.5795585081798578</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.1274820482729145</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.964831773732565</v>
+        <v>-5.710515682576069</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5705143042805916</v>
+        <v>0.6722407407431898</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.1274820482729145</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.788939681265132</v>
+        <v>-5.534623590108637</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6444702647882132</v>
+        <v>0.7461967012508115</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.1274820482729145</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.617493218242669</v>
+        <v>-5.363177127086174</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7263763560517527</v>
+        <v>0.8281027925143505</v>
       </c>
       <c r="F1921" t="n">
         <v>0.04396441474954865</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.54320365250433</v>
+        <v>-5.288887561347835</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7551126599633853</v>
+        <v>0.8568390964259831</v>
       </c>
       <c r="F1922" t="n">
         <v>0.1182539804878879</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.479567910270395</v>
+        <v>-5.2252518191139</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7852617579112762</v>
+        <v>0.886988194373874</v>
       </c>
       <c r="F1923" t="n">
         <v>0.1818897227218225</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.368141150944475</v>
+        <v>-5.11382505978798</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8110267204254398</v>
+        <v>0.912753156888038</v>
       </c>
       <c r="F1924" t="n">
         <v>0.1818897227218225</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.378643774009764</v>
+        <v>-5.124327682853269</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8085687478242018</v>
+        <v>0.9102951842867997</v>
       </c>
       <c r="F1925" t="n">
         <v>0.1713870996565336</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.306401205838569</v>
+        <v>-5.052085114682074</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8413950889274999</v>
+        <v>0.9431215253900977</v>
       </c>
       <c r="F1926" t="n">
         <v>0.1713870996565336</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879963</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.288687518960704</v>
+        <v>-5.034371427804209</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8491591475959859</v>
+        <v>0.9508855840585837</v>
       </c>
       <c r="F1927" t="n">
         <v>0.1745684285534504</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.251427831567751</v>
+        <v>-4.925566542324482</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8610610937731606</v>
+        <v>0.9914056094704682</v>
       </c>
       <c r="F1928" t="n">
         <v>0.1745684285534504</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.031407033530741</v>
+        <v>-4.705545744287472</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.950648449998579</v>
+        <v>1.080992965695887</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3157882736214306</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.898539344467463</v>
+        <v>-4.572678055224194</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.019689708425713</v>
+        <v>1.150034224123021</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3157882736214306</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.778366261102964</v>
+        <v>-4.452504971859695</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.068904786211815</v>
+        <v>1.199249301909122</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4359613569859296</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.633694116003227</v>
+        <v>-4.307832826759958</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.136861746813149</v>
+        <v>1.267206262510457</v>
       </c>
       <c r="F1932" t="n">
         <v>0.580633502085667</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.693568943360919</v>
+        <v>-4.36770765411765</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.098949307271498</v>
+        <v>1.229293822968806</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5207586747279749</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.573748712450082</v>
+        <v>-4.247887423206813</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.162166568870042</v>
+        <v>1.292511084567349</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5207586747279749</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.576218418911888</v>
+        <v>-4.250357129668619</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.068822885607761</v>
+        <v>1.199167401305068</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5182889682661687</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.644588605235898</v>
+        <v>-4.318727315992629</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9607366725634581</v>
+        <v>1.091081188260766</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5275646673023836</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.658376658082945</v>
+        <v>-4.332515368839676</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9456581600565308</v>
+        <v>1.076002675753838</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5275646673023836</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.713896733975535</v>
+        <v>-4.388035444732266</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.060480966391697</v>
+        <v>1.190825482089005</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5275646673023836</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.538422474183065</v>
+        <v>-4.212561184939796</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.135237902300473</v>
+        <v>1.265582417997781</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5275646673023836</v>
@@ -46171,10 +46171,10 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.649358726824314</v>
+        <v>-4.323497437581045</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.06660543000518</v>
+        <v>1.196949945702488</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5275646673023836</v>
@@ -46194,10 +46194,10 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.615695181352032</v>
+        <v>-4.289833892108763</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.008609161595543</v>
+        <v>1.138953677292851</v>
       </c>
       <c r="F1941" t="n">
         <v>0.5612282127746655</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.555842562148309</v>
+        <v>-4.229981272905039</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.042722595709165</v>
+        <v>1.173067111406472</v>
       </c>
       <c r="F1942" t="n">
         <v>0.5612282127746655</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.469599099121931</v>
+        <v>-4.143737809878662</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.072166251493576</v>
+        <v>1.202510767190884</v>
       </c>
       <c r="F1943" t="n">
         <v>0.5612282127746655</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.514905918520911</v>
+        <v>-4.189044629277642</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.04581929917851</v>
+        <v>1.176163814875817</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5204180497654347</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.543939023223212</v>
+        <v>-4.218077733979943</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.034757930330691</v>
+        <v>1.165102446027999</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5204180497654347</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.451128541772352</v>
+        <v>-4.125267252529083</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.0011548148024</v>
+        <v>1.131499330499708</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6132285312162941</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.49551801110178</v>
+        <v>-4.169656721858511</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9852725029952303</v>
+        <v>1.115617018692538</v>
       </c>
       <c r="F1947" t="n">
         <v>0.5688390618868664</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.612059616207122</v>
+        <v>-4.286198326963853</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9337315694648163</v>
+        <v>1.064076085162124</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4522974567815236</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.499682615024449</v>
+        <v>-4.17382132578118</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9841736657685527</v>
+        <v>1.11451818146586</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4522974567815236</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.527463012925802</v>
+        <v>-4.201601723682533</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9845587083765506</v>
+        <v>1.114903224073858</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4245170588801706</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.64584368565594</v>
+        <v>-4.319982396412671</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7755621592851485</v>
+        <v>0.9059066749824563</v>
       </c>
       <c r="F1951" t="n">
         <v>0.3572992067291944</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.754457764099271</v>
+        <v>-4.428596474856002</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8522661886270217</v>
+        <v>0.9826107043243293</v>
       </c>
       <c r="F1952" t="n">
         <v>0.3572992067291944</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.719048725851128</v>
+        <v>-4.393187436607859</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.880942830028602</v>
+        <v>1.01128734572591</v>
       </c>
       <c r="F1953" t="n">
         <v>0.3572992067291944</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.680665063292977</v>
+        <v>-4.354803774049708</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.893715736394231</v>
+        <v>1.024060252091539</v>
       </c>
       <c r="F1954" t="n">
         <v>0.3956828692873455</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.503548733257811</v>
+        <v>-4.177687444014542</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9612912972535994</v>
+        <v>1.091635812950907</v>
       </c>
       <c r="F1955" t="n">
         <v>0.3956828692873455</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.548640978091357</v>
+        <v>-4.222779688848088</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9439377910820941</v>
+        <v>1.074282306779402</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3337868261179557</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.369265556852589</v>
+        <v>-4.04340426760932</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.009474934884016</v>
+        <v>1.139819450581323</v>
       </c>
       <c r="F1957" t="n">
         <v>0.4905635842886744</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.414279770373195</v>
+        <v>-4.088418481129926</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9722767048073631</v>
+        <v>1.102621220504671</v>
       </c>
       <c r="F1958" t="n">
         <v>0.4602146889740698</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.68128428064563</v>
+        <v>-4.355422991402361</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8711664630373348</v>
+        <v>1.001510978734642</v>
       </c>
       <c r="F1959" t="n">
         <v>0.2658516509311212</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.782482062082803</v>
+        <v>-4.456620772839534</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8298912723589671</v>
+        <v>0.9602357880562749</v>
       </c>
       <c r="F1960" t="n">
         <v>0.197442837385802</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.77597109546849</v>
+        <v>-4.450109806225221</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8300956205590089</v>
+        <v>0.9604401362563166</v>
       </c>
       <c r="F1961" t="n">
         <v>0.197442837385802</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.756932967761193</v>
+        <v>-4.431071678517924</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8342355908501728</v>
+        <v>0.9645801065474804</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1392592260546075</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.788059598911811</v>
+        <v>-4.462198309668542</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9410793400241158</v>
+        <v>1.071423855721423</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1392592260546075</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.801926360245729</v>
+        <v>-4.47606507100246</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9363659644766822</v>
+        <v>1.06671048017399</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1014013093207846</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789119</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.757122188705799</v>
+        <v>-4.43126089946253</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9602961634895801</v>
+        <v>1.090640679186888</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1014013093207846</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.609379218470797</v>
+        <v>-4.283517929227528</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9173435728607806</v>
+        <v>1.047688088558088</v>
       </c>
       <c r="F1966" t="n">
         <v>0.2692086665556677</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.693200439745495</v>
+        <v>-4.367339150502226</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8866087058823822</v>
+        <v>1.01695322157969</v>
       </c>
       <c r="F1967" t="n">
         <v>0.2692086665556677</v>
@@ -46815,10 +46815,10 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.687047733692711</v>
+        <v>-4.361186444449442</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8897321366951543</v>
+        <v>1.020076652392462</v>
       </c>
       <c r="F1968" t="n">
         <v>0.275361372608452</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.703857031843213</v>
+        <v>-4.377995742599944</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8820888941750638</v>
+        <v>1.012433409872371</v>
       </c>
       <c r="F1969" t="n">
         <v>0.2585520744579504</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.64155903306709</v>
+        <v>-4.315697743823821</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9733436474823336</v>
+        <v>1.103688163179641</v>
       </c>
       <c r="F1970" t="n">
         <v>0.2585520744579504</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.439768835401932</v>
+        <v>-4.113907546158663</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8563517282625237</v>
+        <v>0.9866962439598315</v>
       </c>
       <c r="F1971" t="n">
         <v>0.4565702666271048</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.490655548088127</v>
+        <v>-4.164794258844858</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9062872755102211</v>
+        <v>1.036631791207529</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4056835539409102</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.588396092713102</v>
+        <v>-4.262534803469832</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8818187937762749</v>
+        <v>1.012163309473583</v>
       </c>
       <c r="F1973" t="n">
         <v>0.38979427580793</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.648605390718386</v>
+        <v>-4.322744101475117</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8562710553988326</v>
+        <v>0.9866155710961404</v>
       </c>
       <c r="F1974" t="n">
         <v>0.3295849778026455</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.57218334428646</v>
+        <v>-4.246322055043191</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8853314920115321</v>
+        <v>1.01567600770884</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3295849778026455</v>
@@ -46999,10 +46999,10 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.527810212647891</v>
+        <v>-4.201948923404622</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9029436121023957</v>
+        <v>1.033288127799703</v>
       </c>
       <c r="F1976" t="n">
         <v>0.3739581094412141</v>
@@ -47022,10 +47022,10 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.550290563506776</v>
+        <v>-4.224429274263507</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8883452658974322</v>
+        <v>1.01868978159474</v>
       </c>
       <c r="F1977" t="n">
         <v>0.3739581094412141</v>
@@ -47045,10 +47045,10 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.50263483294572</v>
+        <v>-4.176773543702451</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9137893151496592</v>
+        <v>1.044133830846967</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4216138400022698</v>
@@ -47068,10 +47068,10 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.402116674446965</v>
+        <v>-4.076255385203696</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9588889519238859</v>
+        <v>1.089233467621193</v>
       </c>
       <c r="F1979" t="n">
         <v>0.5221319985010243</v>
@@ -47091,10 +47091,10 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.462783264849355</v>
+        <v>-4.136921975606086</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9213769882388023</v>
+        <v>1.05172150393611</v>
       </c>
       <c r="F1980" t="n">
         <v>0.4404336817824906</v>
@@ -47114,10 +47114,10 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.417944863240956</v>
+        <v>-4.092083573997687</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9434100514927903</v>
+        <v>1.073754567190098</v>
       </c>
       <c r="F1981" t="n">
         <v>0.4449771147273601</v>
@@ -47137,10 +47137,10 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.437443319482965</v>
+        <v>-4.111582030239695</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9397716086270651</v>
+        <v>1.070116124324373</v>
       </c>
       <c r="F1982" t="n">
         <v>0.3968924734474558</v>
@@ -47160,10 +47160,10 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.393240482397064</v>
+        <v>-4.067379193153795</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9633323459892624</v>
+        <v>1.09367686168657</v>
       </c>
       <c r="F1983" t="n">
         <v>0.4410953105333563</v>
@@ -47183,10 +47183,10 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.430219510060507</v>
+        <v>-4.104358220817238</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9469507353931328</v>
+        <v>1.07729525109044</v>
       </c>
       <c r="F1984" t="n">
         <v>0.4780692123246868</v>
@@ -47206,10 +47206,10 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.271928092521235</v>
+        <v>-3.946066803277966</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.061515067591881</v>
+        <v>1.191859583289189</v>
       </c>
       <c r="F1985" t="n">
         <v>0.4780692123246868</v>
@@ -47229,10 +47229,10 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.064286088886758</v>
+        <v>-3.738424799643489</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.143012573639925</v>
+        <v>1.273357089337233</v>
       </c>
       <c r="F1986" t="n">
         <v>0.685711215959163</v>
@@ -47252,10 +47252,10 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.013253996164231</v>
+        <v>-3.687392706920961</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.158373638967206</v>
+        <v>1.288718154664514</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7367433086816909</v>
@@ -47275,10 +47275,10 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.948029815037025</v>
+        <v>-3.622168525793755</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.201650715510793</v>
+        <v>1.331995231208101</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8019674898088965</v>
@@ -47298,10 +47298,10 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.910602794965892</v>
+        <v>-3.584741505722622</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.212582495838527</v>
+        <v>1.342927011535835</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8072190278380782</v>
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.9307144510006</v>
+        <v>-3.671194734737349</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.205794625755884</v>
+        <v>1.309602512261184</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8182463728354974</v>
+        <v>0.818770544370965</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.26938465417117</v>
+        <v>3.26969915709245</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636282</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.876969636573395</v>
+        <v>-3.617449920310144</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.387850322547977</v>
+        <v>1.491658209053277</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8283096822759594</v>
+        <v>0.8288338538114269</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.435980410856658</v>
+        <v>3.436294913777938</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.802187375548383</v>
+        <v>-3.542667659285132</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.537876136175799</v>
+        <v>1.641684022681099</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.903091943300972</v>
+        <v>0.9036161148364396</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.600962676689483</v>
+        <v>3.601277179610763</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.776103291284575</v>
+        <v>-3.516583575021324</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.540017745895181</v>
+        <v>1.643825632400481</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.903091943300972</v>
+        <v>0.9036161148364396</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.592670652703342</v>
+        <v>3.592985155624622</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.697972110435628</v>
+        <v>-3.438452394172377</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.569463413818539</v>
+        <v>1.67327130032384</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9772687541846565</v>
+        <v>0.9777929257201241</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.635369934817332</v>
+        <v>3.635684437738612</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.689079649042345</v>
+        <v>-3.429559932779094</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.590574804102644</v>
+        <v>1.694382690607944</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9772687541846565</v>
+        <v>0.9777929257201241</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.652924340544123</v>
+        <v>3.653238843465404</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.857555766012223</v>
+        <v>-3.598036049748972</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.515039404719277</v>
+        <v>1.618847291224577</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9493209184680758</v>
+        <v>0.9498450900035433</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.628010686518759</v>
+        <v>3.628325189440039</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.159756237150639</v>
+        <v>-2.900236520887389</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.775428913451772</v>
+        <v>1.879236799957072</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8789728590976651</v>
+        <v>0.8794970306331327</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.567071548084374</v>
+        <v>3.567386051005655</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.137035133467487</v>
+        <v>-2.877515417204236</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.775181377421937</v>
+        <v>1.878989263927238</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8789728590976651</v>
+        <v>0.8794970306331327</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.557735570581279</v>
+        <v>3.558050073502559</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.266236946761529</v>
+        <v>-3.006717230498279</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.882406777955489</v>
+        <v>1.98621466446079</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7497710458036229</v>
+        <v>0.7502952173390904</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.639120608456023</v>
+        <v>3.639435111377303</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.421017953539785</v>
+        <v>-3.161498237276534</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.857572197737834</v>
+        <v>1.961380084243134</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7164033717491467</v>
+        <v>0.7169275432846143</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.656177826516983</v>
+        <v>3.656492329438264</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.413963263324611</v>
+        <v>-3.154443547061361</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.857069429813448</v>
+        <v>1.960877316318749</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7234580619643205</v>
+        <v>0.7239822334997881</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.657085996635633</v>
+        <v>3.657400499556913</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.387012038998123</v>
+        <v>-3.127492322734873</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.877856073188785</v>
+        <v>1.981663959694085</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7383384079920396</v>
+        <v>0.7388625795275072</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.676020357897006</v>
+        <v>3.676334860818286</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.52296504705444</v>
+        <v>-3.263445330791189</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.007578002111218</v>
+        <v>2.111385888616518</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7383384079920396</v>
+        <v>0.7388625795275072</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.860123490041965</v>
+        <v>3.860437992963246</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.545373164859312</v>
+        <v>-3.285853448596061</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.990731449892262</v>
+        <v>2.094539336397563</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7383384079920396</v>
+        <v>0.7388625795275072</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.852240184944959</v>
+        <v>3.852554687866239</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.693378932338711</v>
+        <v>-3.433859216075461</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.93358314245014</v>
+        <v>2.03739102895544</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6516113991284982</v>
+        <v>0.6521355706639658</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.802257979176471</v>
+        <v>3.802572482097752</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.702819858227241</v>
+        <v>-3.443300141963991</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.986060489816575</v>
+        <v>2.089868376321875</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7740385166718896</v>
+        <v>0.7745626882073572</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.931967967424353</v>
+        <v>3.932282470345633</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.755093465562882</v>
+        <v>-3.495573749299632</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.968042141427619</v>
+        <v>2.07185002793292</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7217649093362484</v>
+        <v>0.7222890808717159</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.903494897568269</v>
+        <v>3.90380940048955</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.831423443163788</v>
+        <v>-3.571903726900538</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.935621963281033</v>
+        <v>2.039429849786333</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7217649093362484</v>
+        <v>0.7222890808717159</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.901606710462044</v>
+        <v>3.901921213383325</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-4.033677163488142</v>
+        <v>-3.774157447224891</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.849540704754153</v>
+        <v>1.953348591259454</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5195111890118949</v>
+        <v>0.5200353605473624</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.775074707870295</v>
+        <v>3.775389210791575</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-4.195245589015397</v>
+        <v>-3.935725872752146</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.783347344753404</v>
+        <v>1.887155231258704</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3927282652140155</v>
+        <v>0.3932524367494831</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.697438963801719</v>
+        <v>3.697753466723</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.32754688111295</v>
+        <v>-4.0680271648497</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.743500234780301</v>
+        <v>1.847308121285601</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3927282652140155</v>
+        <v>0.3932524367494831</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.710512370667638</v>
+        <v>3.710826873588918</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763529</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.32910852392781</v>
+        <v>-4.06958880766456</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.742875577654357</v>
+        <v>1.846683464159657</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3927282652140155</v>
+        <v>0.3932524367494831</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.710512370667638</v>
+        <v>3.710826873588918</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392112</v>
+        <v>3.715834055392114</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.357009311037283</v>
+        <v>-4.097489594774032</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.73023930393757</v>
+        <v>1.83404719044287</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3581313410710807</v>
+        <v>0.3586555126065483</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.688278257308879</v>
+        <v>3.68859276023016</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172523</v>
+        <v>3.684909939172525</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.479535413740177</v>
+        <v>-4.220015697476926</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.677993306833611</v>
+        <v>1.781801193338912</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2356052383681868</v>
+        <v>0.2361294099036544</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.611527039664342</v>
+        <v>3.611841542585622</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971074</v>
+        <v>3.619362241971076</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.710049909925766</v>
+        <v>-4.450530193662515</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.65249346794988</v>
+        <v>1.75630135445518</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.005090742182598085</v>
+        <v>0.005614913718065662</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.539924301543492</v>
+        <v>3.540238804464773</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199802</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.96677072792059</v>
+        <v>-4.707251011657339</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.690116859753797</v>
+        <v>1.793924746259097</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.1027996604257492</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.61518727605905</v>
+        <v>3.615501778980331</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622232</v>
+        <v>3.668303164622234</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-5.12075714569673</v>
+        <v>-4.86123742943348</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.69750256178898</v>
+        <v>1.801310448294281</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.1027996604257492</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.68416754520469</v>
+        <v>3.68448204812597</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808524</v>
+        <v>3.619937176808526</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-5.070235241869065</v>
+        <v>-4.810715525605814</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.703762525440168</v>
+        <v>1.807570411945468</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.1027996604257492</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.670218747324811</v>
+        <v>3.670533250246091</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.65634689399489</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.322710395876789</v>
+        <v>-5.063190679613538</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.614642952892492</v>
+        <v>1.718450839397792</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.1027996604257492</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.682089236380225</v>
+        <v>3.682403739301505</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358294</v>
+        <v>3.674042696358296</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.592183197798497</v>
+        <v>-5.332663481535246</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.508064366642752</v>
+        <v>1.611872253148052</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.1027996604257492</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.683299770899168</v>
+        <v>3.683614273820449</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637083</v>
+        <v>3.663523617637085</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.749727269527939</v>
+        <v>-5.490207553264688</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.449168480178297</v>
+        <v>1.552976366683597</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1702256371014912</v>
+        <v>-0.1697014655660237</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.647280430042325</v>
+        <v>3.647594932963606</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.65216331330134</v>
+        <v>3.652163313301341</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-6.027691665111212</v>
+        <v>-5.768171948847962</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.333060574681177</v>
+        <v>1.436868461186477</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2598453713869755</v>
+        <v>-0.2593211998515079</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.588586442207224</v>
+        <v>3.588900945128505</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215466</v>
+        <v>3.667976467215467</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-6.144659357750103</v>
+        <v>-5.885139641486853</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.448477554324665</v>
+        <v>1.552285440829965</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2598453713869755</v>
+        <v>-0.2593211998515079</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.750790498906268</v>
+        <v>3.751105001827549</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456688</v>
+        <v>3.69655362845669</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.229377299971056</v>
+        <v>-5.969857583707806</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.409437015400098</v>
+        <v>1.513244901905398</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.3449614003150219</v>
+        <v>-0.3444372287795543</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.694567519513255</v>
+        <v>3.694882022434535</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253284</v>
+        <v>3.750058176253285</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.31131211823994</v>
+        <v>-6.051792401976689</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.386892505661035</v>
+        <v>1.490700392166336</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3548961459021021</v>
+        <v>-0.3543719743666345</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.698836089729498</v>
+        <v>3.699150592650778</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717828</v>
+        <v>3.783647027717829</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.257573944839677</v>
+        <v>-5.998054228576427</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.417313413477043</v>
+        <v>1.521121299982343</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.30115797250184</v>
+        <v>-0.3006338009663724</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.740004632225557</v>
+        <v>3.740319135146838</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616945</v>
+        <v>3.798310944616946</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.147567661362456</v>
+        <v>-5.888047945099205</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.453468814112107</v>
+        <v>1.557276700617407</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2779534005845647</v>
+        <v>-0.2774292290490972</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.746080262620098</v>
+        <v>3.746394765541378</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203659</v>
+        <v>3.785578085203661</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.004508085621531</v>
+        <v>-5.74498836935828</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.514942655130451</v>
+        <v>1.618750541635751</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2699399739945855</v>
+        <v>-0.2694158024591179</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.75513832929606</v>
+        <v>3.75545283221734</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436925</v>
+        <v>3.777251572436927</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.703061360149693</v>
+        <v>-5.443541643886443</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.642782228201722</v>
+        <v>1.746590114707022</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.03150675147725179</v>
+        <v>0.03203092301271937</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.943267247461698</v>
+        <v>3.943581750382979</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064763</v>
+        <v>3.812650101064765</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.727651604384877</v>
+        <v>-5.468131888121627</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.633917308260359</v>
+        <v>1.737725194765659</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.03150675147725179</v>
+        <v>0.03203092301271937</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.944238425214408</v>
+        <v>3.944552928135689</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859297</v>
+        <v>3.821198342859299</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.676613228378357</v>
+        <v>-5.417093512115106</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.655175563042723</v>
+        <v>1.758983449548023</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.03150675147725179</v>
+        <v>0.03203092301271937</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.945081329594164</v>
+        <v>3.945395832515445</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354682</v>
+        <v>3.831748677354684</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.635473933511726</v>
+        <v>-5.375954217248475</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.69066937986352</v>
+        <v>1.79447726636882</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.07264604634388261</v>
+        <v>0.07317021787935019</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.988803005388288</v>
+        <v>3.989117508309568</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085617</v>
+        <v>3.825767093085618</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.625924540268749</v>
+        <v>-5.265348077168873</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.510673133284645</v>
+        <v>1.654903718524596</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.08219543958685932</v>
+        <v>0.1837763579589522</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.810716637458008</v>
+        <v>3.871665188481264</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462779</v>
+        <v>3.80470312146278</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.756505274799592</v>
+        <v>-5.395928811699716</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.461942883546272</v>
+        <v>1.606173468786222</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.04838529494398319</v>
+        <v>0.05319562342810968</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.735870240813466</v>
+        <v>3.796818791836722</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218597</v>
+        <v>3.775043021218598</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.59200894060863</v>
+        <v>-5.231432477508754</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.512168236298739</v>
+        <v>1.65639882153869</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.04838529494398319</v>
+        <v>0.05319562342810968</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.720297059889549</v>
+        <v>3.781245610912805</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462766</v>
+        <v>3.821044820462768</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.467528459884679</v>
+        <v>-5.106951996784803</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.56114813902475</v>
+        <v>1.7053787242647</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.04838529494398319</v>
+        <v>0.05319562342810968</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.719484770325979</v>
+        <v>3.780433321349234</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533047</v>
+        <v>3.83232118453305</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.477913654774568</v>
+        <v>-5.117337191674692</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.566862840193866</v>
+        <v>1.711093425433817</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.05877048983387251</v>
+        <v>0.04281042853822037</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.723122432517118</v>
+        <v>3.784070983540373</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834429654120417</v>
+        <v>3.834429654120418</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.273910583891343</v>
+        <v>-5.02658271564605</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.719301074323581</v>
+        <v>1.818232221621698</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1452325810493524</v>
+        <v>0.1335649045668621</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.916361280823478</v>
+        <v>3.909360674933983</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.820933520566775</v>
+        <v>3.834852374206423</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.759680923721239</v>
+        <v>3.83756513940301</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.273910583891343</v>
+        <v>-5.02658271564605</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.719301074323581</v>
+        <v>1.818232221621698</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1452325810493524</v>
+        <v>0.1335649045668621</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.752744720707607</v>
+        <v>3.830628936389378</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240728.xlsx
+++ b/tame_output/ON/bt/strategyON_20240728.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>48.2%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>61.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-80.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.3%</t>
+          <t>111.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.9%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-49.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.5%</t>
+          <t>453.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-664.2%</t>
+          <t>-696.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24648.0%</t>
+          <t>-24649.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-194.4%</t>
+          <t>-207.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-116.1%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-210.6%</t>
+          <t>-223.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-63.0%</t>
+          <t>-73.4%</t>
         </is>
       </c>
     </row>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.705545744287472</v>
+        <v>-4.889707833457974</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.080992965695887</v>
+        <v>1.007328130027686</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3157882736214306</v>
+        <v>0.1848635801824742</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.153040651897481</v>
+        <v>3.074485835834107</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.572678055224194</v>
+        <v>-4.857170411599831</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.150034224123021</v>
+        <v>1.036237281572766</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3157882736214306</v>
+        <v>0.1848635801824742</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.168934834699304</v>
+        <v>3.090380018635931</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.452504971859695</v>
+        <v>-4.736997328235332</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.199249301909122</v>
+        <v>1.085452359358868</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4359613569859296</v>
+        <v>0.3050366635469732</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.242184529158306</v>
+        <v>3.163629713094932</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.307832826759958</v>
+        <v>-4.592325183135594</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.267206262510457</v>
+        <v>1.153409319960202</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.580633502085667</v>
+        <v>0.4497088086467106</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.339075918779588</v>
+        <v>3.260521102716214</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.36770765411765</v>
+        <v>-4.652200010493287</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.229293822968806</v>
+        <v>1.115496880418551</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5207586747279749</v>
+        <v>0.3898339812890185</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.289188513766399</v>
+        <v>3.210633697703025</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.247887423206813</v>
+        <v>-4.53237977958245</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.292511084567349</v>
+        <v>1.178714142017095</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5207586747279749</v>
+        <v>0.3898339812890185</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.304477683000607</v>
+        <v>3.225922866937233</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.250357129668619</v>
+        <v>-4.534849486044256</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.199167401305068</v>
+        <v>1.085370458754814</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5182889682661687</v>
+        <v>0.3873642748272123</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.210640058445965</v>
+        <v>3.132085242382591</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.318727315992629</v>
+        <v>-4.603219672368266</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.091081188260766</v>
+        <v>0.9772842457105111</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5275646673023836</v>
+        <v>0.3966399738634273</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.135467339352995</v>
+        <v>3.056912523289621</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.332515368839676</v>
+        <v>-4.617007725215313</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.076002675753838</v>
+        <v>0.9622057332035836</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5275646673023836</v>
+        <v>0.3966399738634273</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.125904047984887</v>
+        <v>3.047349231921513</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.388035444732266</v>
+        <v>-4.672527801107902</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.190825482089005</v>
+        <v>1.07702853953875</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5275646673023836</v>
+        <v>0.3966399738634273</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.262934884677089</v>
+        <v>3.184380068613715</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.212561184939796</v>
+        <v>-4.497053541315433</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.265582417997781</v>
+        <v>1.151785475447526</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5275646673023836</v>
+        <v>0.3966399738634273</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.267502116668877</v>
+        <v>3.188947300605503</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.323497437581045</v>
+        <v>-4.607989793956682</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.196949945702488</v>
+        <v>1.083153003152233</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5275646673023836</v>
+        <v>0.3966399738634273</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.243244145430084</v>
+        <v>3.16468932936671</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.289833892108763</v>
+        <v>-4.574326248484399</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.138953677292851</v>
+        <v>1.025156734742596</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5612282127746655</v>
+        <v>0.4303035193357091</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.191980586114902</v>
+        <v>3.113425770051529</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.229981272905039</v>
+        <v>-4.514473629280676</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.173067111406472</v>
+        <v>1.059270168856218</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5612282127746655</v>
+        <v>0.4303035193357091</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.202152972547035</v>
+        <v>3.123598156483661</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.143737809878662</v>
+        <v>-4.428230166254298</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.202510767190884</v>
+        <v>1.088713824640629</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5612282127746655</v>
+        <v>0.4303035193357091</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.197099243120896</v>
+        <v>3.118544427057521</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.189044629277642</v>
+        <v>-4.473536985653278</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.176163814875817</v>
+        <v>1.062366872325563</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5204180497654347</v>
+        <v>0.3894933563264783</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.164388920759882</v>
+        <v>3.085834104696509</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.218077733979943</v>
+        <v>-4.502570090355579</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.165102446027999</v>
+        <v>1.051305503477744</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5204180497654347</v>
+        <v>0.3894933563264783</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.164940793792984</v>
+        <v>3.08638597772961</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.125267252529083</v>
+        <v>-4.40975960890472</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.131499330499708</v>
+        <v>1.017702387949453</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6132285312162941</v>
+        <v>0.4823038377773377</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.149899774554865</v>
+        <v>3.071344958491491</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.169656721858511</v>
+        <v>-4.454149078234147</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.115617018692538</v>
+        <v>1.001820076142283</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5688390618868664</v>
+        <v>0.43791436844791</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.12513956888181</v>
+        <v>3.046584752818436</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.286198326963853</v>
+        <v>-4.57069068333949</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.064076085162124</v>
+        <v>0.9502791426118691</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4522974567815236</v>
+        <v>0.3213727633425672</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.050290314330327</v>
+        <v>2.971735498266953</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.17382132578118</v>
+        <v>-4.458313682156817</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.11451818146586</v>
+        <v>1.000721238915605</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4522974567815236</v>
+        <v>0.3213727633425672</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.055781610160994</v>
+        <v>2.97722679409762</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.201601723682533</v>
+        <v>-4.486094080058169</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.114903224073858</v>
+        <v>1.001106281523604</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4245170588801706</v>
+        <v>0.2935923654412141</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.050610573188721</v>
+        <v>2.972055757125347</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.319982396412671</v>
+        <v>-4.604474752788308</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9059066749824563</v>
+        <v>0.7921097324322015</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3572992067291944</v>
+        <v>0.2263745132902379</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.848635581898789</v>
+        <v>2.770080765835415</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.428596474856002</v>
+        <v>-4.713088831231639</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9826107043243293</v>
+        <v>0.8688137617740748</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3572992067291944</v>
+        <v>0.2263745132902379</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.968785242617995</v>
+        <v>2.890230426554621</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.393187436607859</v>
+        <v>-4.677679792983496</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.01128734572591</v>
+        <v>0.8974904031756548</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3572992067291944</v>
+        <v>0.2263745132902379</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.983298268720318</v>
+        <v>2.904743452656944</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.354803774049708</v>
+        <v>-4.639296130425345</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.024060252091539</v>
+        <v>0.910263309541284</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3956828692873455</v>
+        <v>0.2647581758483891</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.003747907597577</v>
+        <v>2.925193091534203</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.177687444014542</v>
+        <v>-4.462179800390179</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.091635812950907</v>
+        <v>0.9778388704006522</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3956828692873455</v>
+        <v>0.2647581758483891</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.000476936442879</v>
+        <v>2.921922120379505</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.222779688848088</v>
+        <v>-4.507272045223725</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.074282306779402</v>
+        <v>0.9604853642291471</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3337868261179557</v>
+        <v>0.2028621326789993</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.964022702303158</v>
+        <v>2.885467886239784</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.04340426760932</v>
+        <v>-4.327896623984957</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.139819450581323</v>
+        <v>1.026022508031069</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4905635842886744</v>
+        <v>0.359638890849718</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.051875732512003</v>
+        <v>2.97332091644863</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.088418481129926</v>
+        <v>-4.372910837505563</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.102621220504671</v>
+        <v>0.9888242779544161</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4602146889740698</v>
+        <v>0.3292899955351134</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.01447385065483</v>
+        <v>2.935919034591457</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.355422991402361</v>
+        <v>-4.639915347777998</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.001510978734642</v>
+        <v>0.8877140361843878</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2658516509311212</v>
+        <v>0.1349269574921648</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.903547590168007</v>
+        <v>2.824992774104633</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.456620772839534</v>
+        <v>-4.74111312921517</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9602357880562749</v>
+        <v>0.8464388455060201</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.197442837385802</v>
+        <v>0.06651814394684563</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.861706223937317</v>
+        <v>2.783151407873943</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.450109806225221</v>
+        <v>-4.734602162600858</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9604401362563166</v>
+        <v>0.8466431937060619</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.197442837385802</v>
+        <v>0.06651814394684563</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.859306185491634</v>
+        <v>2.78075136942826</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.431071678517924</v>
+        <v>-4.715564034893561</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9645801065474804</v>
+        <v>0.8507831639972256</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1392592260546075</v>
+        <v>0.008334532615651091</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.820920737901162</v>
+        <v>2.742365921837788</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.462198309668542</v>
+        <v>-4.746690666044179</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.071423855721423</v>
+        <v>0.9576269131711688</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1392592260546075</v>
+        <v>0.008334532615651091</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.940215139535352</v>
+        <v>2.861660323471979</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.47606507100246</v>
+        <v>-4.760557427378097</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.06671048017399</v>
+        <v>0.952913537623735</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1014013093207846</v>
+        <v>-0.02952338411817185</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.918333718481192</v>
+        <v>2.839778902417818</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.43126089946253</v>
+        <v>-4.715753255838167</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.090640679186888</v>
+        <v>0.9768437366366329</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1014013093207846</v>
+        <v>-0.02952338411817185</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.924342248878118</v>
+        <v>2.845787432814744</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.283517929227528</v>
+        <v>-4.568010285603164</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.047688088558088</v>
+        <v>0.9338911460078334</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2692086665556677</v>
+        <v>0.1382839731167113</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.922976884496248</v>
+        <v>2.844422068432873</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.367339150502226</v>
+        <v>-4.651831506877863</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.01695322157969</v>
+        <v>0.9031562790294352</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2692086665556677</v>
+        <v>0.1382839731167113</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.925770506027729</v>
+        <v>2.847215689964354</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.361186444449442</v>
+        <v>-4.645678800825078</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.020076652392462</v>
+        <v>0.9062797098422073</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.275361372608452</v>
+        <v>0.1444366791694956</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.930124478051057</v>
+        <v>2.851569661987683</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.377995742599944</v>
+        <v>-4.66248809897558</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.012433409872371</v>
+        <v>0.8986364673221168</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2585520744579504</v>
+        <v>0.127627381018994</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.919119375900867</v>
+        <v>2.840564559837493</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.315697743823821</v>
+        <v>-4.600190100199458</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.103688163179641</v>
+        <v>0.9898912206293864</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2585520744579504</v>
+        <v>0.127627381018994</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.985454929697688</v>
+        <v>2.906900113634314</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.113907546158663</v>
+        <v>-4.3983999025343</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9866962439598315</v>
+        <v>0.8728993014095767</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4565702666271048</v>
+        <v>0.3256455731881484</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.906557846713307</v>
+        <v>2.828003030649934</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.164794258844858</v>
+        <v>-4.449286615220495</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.036631791207529</v>
+        <v>0.9228348486572742</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4056835539409102</v>
+        <v>0.2747588605019538</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.946316051423766</v>
+        <v>2.867761235360392</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.262534803469832</v>
+        <v>-4.547027159845469</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.012163309473583</v>
+        <v>0.8983663669233279</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.38979427580793</v>
+        <v>0.2588695823689736</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.951410220660021</v>
+        <v>2.872855404596647</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.322744101475117</v>
+        <v>-4.607236457850754</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9866155710961404</v>
+        <v>0.8728186285458857</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3295849778026455</v>
+        <v>0.1986602843636891</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.913820622681522</v>
+        <v>2.835265806618148</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.246322055043191</v>
+        <v>-4.530814411418827</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.01567600770884</v>
+        <v>0.9018790651585848</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3295849778026455</v>
+        <v>0.1986602843636891</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.912312240721451</v>
+        <v>2.833757424658077</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.201948923404622</v>
+        <v>-4.486441279780259</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.033288127799703</v>
+        <v>0.9194911852494485</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3739581094412141</v>
+        <v>0.2430334160022577</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.938798987140028</v>
+        <v>2.860244171076654</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.224429274263507</v>
+        <v>-4.508921630639144</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.01868978159474</v>
+        <v>0.9048928390444853</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3739581094412141</v>
+        <v>0.2430334160022577</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.933192781278619</v>
+        <v>2.854637965215245</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.176773543702451</v>
+        <v>-4.461265900078088</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.044133830846967</v>
+        <v>0.9303368882967122</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4216138400022698</v>
+        <v>0.2906891465633133</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.968167976643056</v>
+        <v>2.889613160579683</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.076255385203696</v>
+        <v>-4.360747741579333</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.089233467621193</v>
+        <v>0.9754365250709389</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5221319985010243</v>
+        <v>0.3912073050620679</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.033371245117034</v>
+        <v>2.95481642905366</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.136921975606086</v>
+        <v>-4.421414331981723</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.05172150393611</v>
+        <v>0.9379245613858553</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4404336817824906</v>
+        <v>0.3095089883435342</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.971106927561786</v>
+        <v>2.892552111498413</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.092083573997687</v>
+        <v>-4.376575930373324</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.073754567190098</v>
+        <v>0.9599576246398431</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4449771147273601</v>
+        <v>0.3140524212884037</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.977930689939337</v>
+        <v>2.899375873875963</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.111582030239695</v>
+        <v>-4.396074386615332</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.070116124324373</v>
+        <v>0.9563191817741179</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3968924734474558</v>
+        <v>0.2659677800084994</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.953240844802472</v>
+        <v>2.874686028739098</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.067379193153795</v>
+        <v>-4.351871549529432</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.09367686168657</v>
+        <v>0.9798799191363152</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4410953105333563</v>
+        <v>0.3101706170943999</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.985642149581849</v>
+        <v>2.907087333518475</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.104358220817238</v>
+        <v>-4.388850577192875</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.07729525109044</v>
+        <v>0.9634983085401858</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4780692123246868</v>
+        <v>0.3471445188857304</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.006236491125895</v>
+        <v>2.927681675062521</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.946066803277966</v>
+        <v>-4.230559159653603</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.191859583289189</v>
+        <v>1.078062640738934</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4780692123246868</v>
+        <v>0.3471445188857304</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.057484256308935</v>
+        <v>2.978929440245561</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321018</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.738424799643489</v>
+        <v>-4.022917156019126</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.273357089337233</v>
+        <v>1.159560146786978</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.685711215959163</v>
+        <v>0.5547865225202065</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.180510163083873</v>
+        <v>3.1019553470205</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.687392706920961</v>
+        <v>-3.971885063296598</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.288718154664514</v>
+        <v>1.174921212114259</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7367433086816909</v>
+        <v>0.6058186152427345</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.20607764695566</v>
+        <v>3.127522830892286</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.622168525793755</v>
+        <v>-3.906660882169392</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.331995231208101</v>
+        <v>1.218198288657846</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8019674898088965</v>
+        <v>0.6710427963699401</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.262399559724689</v>
+        <v>3.183844743661315</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.584741505722622</v>
+        <v>-3.869233862098258</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.342927011535835</v>
+        <v>1.22913006898558</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8072190278380782</v>
+        <v>0.6762943343991218</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.261511454841478</v>
+        <v>3.182956638778104</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.671194734737349</v>
+        <v>-3.889345518132967</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.309602512261184</v>
+        <v>1.222342198902937</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.818770544370965</v>
+        <v>0.687321679396541</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.26969915709245</v>
+        <v>3.190829838107796</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636282</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.617449920310144</v>
+        <v>-3.835600703705762</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.491658209053277</v>
+        <v>1.40439789569503</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8288338538114269</v>
+        <v>0.697384988837003</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.436294913777938</v>
+        <v>3.357425594793284</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.542667659285132</v>
+        <v>-3.760818442680749</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.641684022681099</v>
+        <v>1.554423709322852</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9036161148364396</v>
+        <v>0.7721672498620156</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.601277179610763</v>
+        <v>3.522407860626109</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.516583575021324</v>
+        <v>-3.734734358416941</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.643825632400481</v>
+        <v>1.556565319042234</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9036161148364396</v>
+        <v>0.7721672498620156</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.592985155624622</v>
+        <v>3.514115836639968</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.438452394172377</v>
+        <v>-3.656603177567995</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.67327130032384</v>
+        <v>1.586010986965593</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9777929257201241</v>
+        <v>0.8463440607457001</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.635684437738612</v>
+        <v>3.556815118753958</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959853</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.429559932779094</v>
+        <v>-3.647710716174712</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.694382690607944</v>
+        <v>1.607122377249697</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9777929257201241</v>
+        <v>0.8463440607457001</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.653238843465404</v>
+        <v>3.574369524480749</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945361</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.598036049748972</v>
+        <v>-3.816186833144589</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.618847291224577</v>
+        <v>1.53158697786633</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9498450900035433</v>
+        <v>0.8183962250291194</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.628325189440039</v>
+        <v>3.549455870455385</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782703</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.900236520887389</v>
+        <v>-3.118387304283006</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.879236799957072</v>
+        <v>1.791976486598825</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8794970306331327</v>
+        <v>0.7480481656587086</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.567386051005655</v>
+        <v>3.488516732021</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632632</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.877515417204236</v>
+        <v>-3.095666200599854</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.878989263927238</v>
+        <v>1.791728950568991</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8794970306331327</v>
+        <v>0.7480481656587086</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.558050073502559</v>
+        <v>3.479180754517905</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.006717230498279</v>
+        <v>-3.224868013893896</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.98621466446079</v>
+        <v>1.898954351102543</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7502952173390904</v>
+        <v>0.6188463523646663</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.639435111377303</v>
+        <v>3.560565792392648</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.161498237276534</v>
+        <v>-3.379649020672152</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.961380084243134</v>
+        <v>1.874119770884887</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7169275432846143</v>
+        <v>0.5854786783101902</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.656492329438264</v>
+        <v>3.57762301045361</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.154443547061361</v>
+        <v>-3.372594330456978</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.960877316318749</v>
+        <v>1.873617002960501</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7239822334997881</v>
+        <v>0.592533368525364</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.657400499556913</v>
+        <v>3.578531180572259</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.127492322734873</v>
+        <v>-3.34564310613049</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.981663959694085</v>
+        <v>1.894403646335838</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7388625795275072</v>
+        <v>0.6074137145530831</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.676334860818286</v>
+        <v>3.597465541833632</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.263445330791189</v>
+        <v>-3.481596114186806</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.111385888616518</v>
+        <v>2.024125575258272</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7388625795275072</v>
+        <v>0.6074137145530831</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.860437992963246</v>
+        <v>3.781568673978592</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.285853448596061</v>
+        <v>-3.504004231991678</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.094539336397563</v>
+        <v>2.007279023039316</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7388625795275072</v>
+        <v>0.6074137145530831</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.852554687866239</v>
+        <v>3.773685368881585</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.433859216075461</v>
+        <v>-3.652009999471078</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.03739102895544</v>
+        <v>1.950130715597194</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6521355706639658</v>
+        <v>0.5206867056895417</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.802572482097752</v>
+        <v>3.723703163113097</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.443300141963991</v>
+        <v>-3.661450925359608</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.089868376321875</v>
+        <v>2.002608062963628</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7745626882073572</v>
+        <v>0.6431138232329331</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.932282470345633</v>
+        <v>3.853413151360979</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.495573749299632</v>
+        <v>-3.713724532695249</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.07185002793292</v>
+        <v>1.984589714574673</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7222890808717159</v>
+        <v>0.5908402158972919</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.90380940048955</v>
+        <v>3.824940081504896</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.571903726900538</v>
+        <v>-3.790054510296155</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.039429849786333</v>
+        <v>1.952169536428086</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7222890808717159</v>
+        <v>0.5908402158972919</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.901921213383325</v>
+        <v>3.823051894398671</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.774157447224891</v>
+        <v>-3.992308230620508</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.953348591259454</v>
+        <v>1.866088277901207</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5200353605473624</v>
+        <v>0.3885864955729384</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.775389210791575</v>
+        <v>3.696519891806921</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.935725872752146</v>
+        <v>-4.153876656147763</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.887155231258704</v>
+        <v>1.799894917900457</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3932524367494831</v>
+        <v>0.261803571775059</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.697753466723</v>
+        <v>3.618884147738346</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647102</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.0680271648497</v>
+        <v>-4.286177948245316</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.847308121285601</v>
+        <v>1.760047807927354</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3932524367494831</v>
+        <v>0.261803571775059</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.710826873588918</v>
+        <v>3.631957554604264</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.06958880766456</v>
+        <v>-4.287739591060176</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.846683464159657</v>
+        <v>1.759423150801411</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3932524367494831</v>
+        <v>0.261803571775059</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.710826873588918</v>
+        <v>3.631957554604264</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392114</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.097489594774032</v>
+        <v>-4.315640378169649</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.83404719044287</v>
+        <v>1.746786877084624</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3586555126065483</v>
+        <v>0.2272066476321242</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.68859276023016</v>
+        <v>3.609723441245505</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172525</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.220015697476926</v>
+        <v>-4.438166480872543</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.781801193338912</v>
+        <v>1.694540879980665</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2361294099036544</v>
+        <v>0.1046805449292303</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.611841542585622</v>
+        <v>3.532972223600968</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971076</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.450530193662515</v>
+        <v>-4.668680977058131</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.75630135445518</v>
+        <v>1.669041041096933</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.005614913718065662</v>
+        <v>-0.1258339512563584</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.540238804464773</v>
+        <v>3.461369485480118</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.707251011657339</v>
+        <v>-4.925401795052956</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.793924746259097</v>
+        <v>1.70666443290085</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.1027996604257492</v>
+        <v>-0.2342485254001732</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.615501778980331</v>
+        <v>3.536632459995676</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622234</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.86123742943348</v>
+        <v>-5.079388212829096</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.801310448294281</v>
+        <v>1.714050134936034</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.1027996604257492</v>
+        <v>-0.2342485254001732</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.68448204812597</v>
+        <v>3.605612729141316</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808526</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.810715525605814</v>
+        <v>-5.028866309001431</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.807570411945468</v>
+        <v>1.720310098587221</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.1027996604257492</v>
+        <v>-0.2342485254001732</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.670533250246091</v>
+        <v>3.591663931261437</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.063190679613538</v>
+        <v>-5.281341463009155</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.718450839397792</v>
+        <v>1.631190526039545</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.1027996604257492</v>
+        <v>-0.2342485254001732</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.682403739301505</v>
+        <v>3.603534420316851</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.332663481535246</v>
+        <v>-5.550814264930863</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.611872253148052</v>
+        <v>1.524611939789806</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.1027996604257492</v>
+        <v>-0.2342485254001732</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.683614273820449</v>
+        <v>3.604744954835795</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637085</v>
+        <v>3.663523617637086</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.490207553264688</v>
+        <v>-5.708358336660305</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.552976366683597</v>
+        <v>1.465716053325351</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1697014655660237</v>
+        <v>-0.3011503305404477</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.647594932963606</v>
+        <v>3.568725613978951</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301341</v>
+        <v>3.652163313301342</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.768171948847962</v>
+        <v>-5.986322732243578</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.436868461186477</v>
+        <v>1.34960814782823</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2593211998515079</v>
+        <v>-0.390770064825932</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.588900945128505</v>
+        <v>3.51003162614385</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215467</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.885139641486853</v>
+        <v>-6.208853518922301</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.552285440829965</v>
+        <v>1.422799889855785</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2593211998515079</v>
+        <v>-0.390770064825932</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.751105001827549</v>
+        <v>3.672235682842894</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69655362845669</v>
+        <v>3.696553628456691</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.969857583707806</v>
+        <v>-6.293571461143254</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.513244901905398</v>
+        <v>1.383759350931218</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.3444372287795543</v>
+        <v>-0.4758860937539783</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.694882022434535</v>
+        <v>3.616012703449881</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253285</v>
+        <v>3.750058176253287</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.051792401976689</v>
+        <v>-6.375506279412138</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.490700392166336</v>
+        <v>1.361214841192156</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3543719743666345</v>
+        <v>-0.4858208393410585</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.699150592650778</v>
+        <v>3.620281273666124</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717829</v>
+        <v>3.783647027717831</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.998054228576427</v>
+        <v>-6.321768106011875</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.521121299982343</v>
+        <v>1.391635749008163</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.3006338009663724</v>
+        <v>-0.4320826659407964</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.740319135146838</v>
+        <v>3.661449816162183</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616946</v>
+        <v>3.798310944616947</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.888047945099205</v>
+        <v>-6.211761822534654</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.557276700617407</v>
+        <v>1.427791149643228</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2774292290490972</v>
+        <v>-0.4088780940235212</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.746394765541378</v>
+        <v>3.667525446556724</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.74498836935828</v>
+        <v>-6.068702246793729</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.618750541635751</v>
+        <v>1.489264990661572</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2694158024591179</v>
+        <v>-0.4008646674335419</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.75545283221734</v>
+        <v>3.676583513232686</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.443541643886443</v>
+        <v>-5.767255521321891</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.746590114707022</v>
+        <v>1.617104563732843</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.03203092301271937</v>
+        <v>-0.09941794196170467</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.943581750382979</v>
+        <v>3.864712431398324</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.468131888121627</v>
+        <v>-5.791845765557075</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.737725194765659</v>
+        <v>1.608239643791479</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.03203092301271937</v>
+        <v>-0.09941794196170467</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.944552928135689</v>
+        <v>3.865683609151034</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.417093512115106</v>
+        <v>-5.740807389550555</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.758983449548023</v>
+        <v>1.629497898573843</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.03203092301271937</v>
+        <v>-0.09941794196170467</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.945395832515445</v>
+        <v>3.86652651353079</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.375954217248475</v>
+        <v>-5.699668094683924</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.79447726636882</v>
+        <v>1.664991715394641</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.07317021787935019</v>
+        <v>-0.05827864709507385</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.989117508309568</v>
+        <v>3.910248189324914</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085618</v>
+        <v>3.825767093085619</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.265348077168873</v>
+        <v>-5.589061954604322</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.654903718524596</v>
+        <v>1.525418167550416</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1837763579589522</v>
+        <v>0.05232749298452816</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.871665188481264</v>
+        <v>3.79279586949661</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80470312146278</v>
+        <v>3.804703121462781</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.395928811699716</v>
+        <v>-5.719642689135164</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.606173468786222</v>
+        <v>1.476687917812043</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.05319562342810968</v>
+        <v>-0.07825324154631436</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.796818791836722</v>
+        <v>3.717949472852068</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218598</v>
+        <v>3.775043021218599</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.231432477508754</v>
+        <v>-5.555146354944203</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.65639882153869</v>
+        <v>1.52691327056451</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.05319562342810968</v>
+        <v>-0.07825324154631436</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.781245610912805</v>
+        <v>3.70237629192815</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.106951996784803</v>
+        <v>-5.430665874220251</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.7053787242647</v>
+        <v>1.575893173290521</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.05319562342810968</v>
+        <v>-0.07825324154631436</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.780433321349234</v>
+        <v>3.70156400236458</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83232118453305</v>
+        <v>3.832321184533049</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.117337191674692</v>
+        <v>-5.441051069110141</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.711093425433817</v>
+        <v>1.581607874459637</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.04281042853822037</v>
+        <v>-0.08863843643620367</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.784070983540373</v>
+        <v>3.705201664555719</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.02658271564605</v>
+        <v>-5.350296593081499</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.818232221621698</v>
+        <v>1.688746670647519</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1335649045668621</v>
+        <v>0.002116039592438057</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.909360674933983</v>
+        <v>3.830491355949329</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.834852374206423</v>
+        <v>3.762794790075265</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.83756513940301</v>
+        <v>3.73328674058193</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.02658271564605</v>
+        <v>-5.350296593081499</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.818232221621698</v>
+        <v>1.688746670647519</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1335649045668621</v>
+        <v>0.002116039592438057</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.830628936389378</v>
+        <v>3.726350537568297</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240728.xlsx
+++ b/tame_output/ON/bt/strategyON_20240728.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>51.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>66.4%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.8%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.1%</t>
+          <t>111.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>126.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-47.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.8%</t>
+          <t>454.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-696.6%</t>
+          <t>-664.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,42 +1140,42 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24649.4%</t>
+          <t>-24649.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-207.3%</t>
+          <t>-194.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-123.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-223.8%</t>
+          <t>-198.3%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-68.7%</t>
         </is>
       </c>
     </row>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.889707833457974</v>
+        <v>-4.705545744287472</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.007328130027686</v>
+        <v>1.080992965695887</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.1848635801824742</v>
+        <v>0.3157882736214306</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.074485835834107</v>
+        <v>3.153040651897481</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.857170411599831</v>
+        <v>-4.572678055224194</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.036237281572766</v>
+        <v>1.150034224123021</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.1848635801824742</v>
+        <v>0.3157882736214306</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.090380018635931</v>
+        <v>3.168934834699304</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.736997328235332</v>
+        <v>-4.452504971859695</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.085452359358868</v>
+        <v>1.199249301909122</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3050366635469732</v>
+        <v>0.4359613569859296</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.163629713094932</v>
+        <v>3.242184529158306</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.592325183135594</v>
+        <v>-4.307832826759958</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.153409319960202</v>
+        <v>1.267206262510457</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4497088086467106</v>
+        <v>0.580633502085667</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.260521102716214</v>
+        <v>3.339075918779588</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.652200010493287</v>
+        <v>-4.36770765411765</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.115496880418551</v>
+        <v>1.229293822968806</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.3898339812890185</v>
+        <v>0.5207586747279749</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.210633697703025</v>
+        <v>3.289188513766399</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.53237977958245</v>
+        <v>-4.247887423206813</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.178714142017095</v>
+        <v>1.292511084567349</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.3898339812890185</v>
+        <v>0.5207586747279749</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.225922866937233</v>
+        <v>3.304477683000607</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.534849486044256</v>
+        <v>-4.250357129668619</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.085370458754814</v>
+        <v>1.199167401305068</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.3873642748272123</v>
+        <v>0.5182889682661687</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.132085242382591</v>
+        <v>3.210640058445965</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.603219672368266</v>
+        <v>-4.318727315992629</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9772842457105111</v>
+        <v>1.091081188260766</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.3966399738634273</v>
+        <v>0.5275646673023836</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.056912523289621</v>
+        <v>3.135467339352995</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.617007725215313</v>
+        <v>-4.332515368839676</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9622057332035836</v>
+        <v>1.076002675753838</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.3966399738634273</v>
+        <v>0.5275646673023836</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.047349231921513</v>
+        <v>3.125904047984887</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.672527801107902</v>
+        <v>-4.388035444732266</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.07702853953875</v>
+        <v>1.190825482089005</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.3966399738634273</v>
+        <v>0.5275646673023836</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.184380068613715</v>
+        <v>3.262934884677089</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.497053541315433</v>
+        <v>-4.212561184939796</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.151785475447526</v>
+        <v>1.265582417997781</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.3966399738634273</v>
+        <v>0.5275646673023836</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.188947300605503</v>
+        <v>3.267502116668877</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.607989793956682</v>
+        <v>-4.323497437581045</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.083153003152233</v>
+        <v>1.196949945702488</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.3966399738634273</v>
+        <v>0.5275646673023836</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.16468932936671</v>
+        <v>3.243244145430084</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.574326248484399</v>
+        <v>-4.289833892108763</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.025156734742596</v>
+        <v>1.138953677292851</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4303035193357091</v>
+        <v>0.5612282127746655</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.113425770051529</v>
+        <v>3.191980586114902</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.514473629280676</v>
+        <v>-4.229981272905039</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.059270168856218</v>
+        <v>1.173067111406472</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4303035193357091</v>
+        <v>0.5612282127746655</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.123598156483661</v>
+        <v>3.202152972547035</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.428230166254298</v>
+        <v>-4.143737809878662</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.088713824640629</v>
+        <v>1.202510767190884</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4303035193357091</v>
+        <v>0.5612282127746655</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.118544427057521</v>
+        <v>3.197099243120896</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.473536985653278</v>
+        <v>-4.189044629277642</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.062366872325563</v>
+        <v>1.176163814875817</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3894933563264783</v>
+        <v>0.5204180497654347</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.085834104696509</v>
+        <v>3.164388920759882</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.502570090355579</v>
+        <v>-4.218077733979943</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.051305503477744</v>
+        <v>1.165102446027999</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3894933563264783</v>
+        <v>0.5204180497654347</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.08638597772961</v>
+        <v>3.164940793792984</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.40975960890472</v>
+        <v>-4.125267252529083</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.017702387949453</v>
+        <v>1.131499330499708</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4823038377773377</v>
+        <v>0.6132285312162941</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.071344958491491</v>
+        <v>3.149899774554865</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.454149078234147</v>
+        <v>-4.169656721858511</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.001820076142283</v>
+        <v>1.115617018692538</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.43791436844791</v>
+        <v>0.5688390618868664</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.046584752818436</v>
+        <v>3.12513956888181</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.57069068333949</v>
+        <v>-4.286198326963853</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9502791426118691</v>
+        <v>1.064076085162124</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.3213727633425672</v>
+        <v>0.4522974567815236</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.971735498266953</v>
+        <v>3.050290314330327</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.458313682156817</v>
+        <v>-4.17382132578118</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.000721238915605</v>
+        <v>1.11451818146586</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.3213727633425672</v>
+        <v>0.4522974567815236</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.97722679409762</v>
+        <v>3.055781610160994</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.486094080058169</v>
+        <v>-4.201601723682533</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.001106281523604</v>
+        <v>1.114903224073858</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.2935923654412141</v>
+        <v>0.4245170588801706</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.972055757125347</v>
+        <v>3.050610573188721</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.604474752788308</v>
+        <v>-4.319982396412671</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7921097324322015</v>
+        <v>0.9059066749824563</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.2263745132902379</v>
+        <v>0.3572992067291944</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.770080765835415</v>
+        <v>2.848635581898789</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.713088831231639</v>
+        <v>-4.428596474856002</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8688137617740748</v>
+        <v>0.9826107043243293</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.2263745132902379</v>
+        <v>0.3572992067291944</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.890230426554621</v>
+        <v>2.968785242617995</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.677679792983496</v>
+        <v>-4.393187436607859</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8974904031756548</v>
+        <v>1.01128734572591</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.2263745132902379</v>
+        <v>0.3572992067291944</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.904743452656944</v>
+        <v>2.983298268720318</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.639296130425345</v>
+        <v>-4.354803774049708</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.910263309541284</v>
+        <v>1.024060252091539</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.2647581758483891</v>
+        <v>0.3956828692873455</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.925193091534203</v>
+        <v>3.003747907597577</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.462179800390179</v>
+        <v>-4.177687444014542</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9778388704006522</v>
+        <v>1.091635812950907</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.2647581758483891</v>
+        <v>0.3956828692873455</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.921922120379505</v>
+        <v>3.000476936442879</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.507272045223725</v>
+        <v>-4.222779688848088</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9604853642291471</v>
+        <v>1.074282306779402</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2028621326789993</v>
+        <v>0.3337868261179557</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.885467886239784</v>
+        <v>2.964022702303158</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.327896623984957</v>
+        <v>-4.04340426760932</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.026022508031069</v>
+        <v>1.139819450581323</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.359638890849718</v>
+        <v>0.4905635842886744</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.97332091644863</v>
+        <v>3.051875732512003</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.372910837505563</v>
+        <v>-4.088418481129926</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9888242779544161</v>
+        <v>1.102621220504671</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.3292899955351134</v>
+        <v>0.4602146889740698</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.935919034591457</v>
+        <v>3.01447385065483</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.639915347777998</v>
+        <v>-4.355422991402361</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8877140361843878</v>
+        <v>1.001510978734642</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.1349269574921648</v>
+        <v>0.2658516509311212</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.824992774104633</v>
+        <v>2.903547590168007</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.74111312921517</v>
+        <v>-4.456620772839534</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8464388455060201</v>
+        <v>0.9602357880562749</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.06651814394684563</v>
+        <v>0.197442837385802</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.783151407873943</v>
+        <v>2.861706223937317</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.734602162600858</v>
+        <v>-4.450109806225221</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8466431937060619</v>
+        <v>0.9604401362563166</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.06651814394684563</v>
+        <v>0.197442837385802</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.78075136942826</v>
+        <v>2.859306185491634</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.715564034893561</v>
+        <v>-4.431071678517924</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8507831639972256</v>
+        <v>0.9645801065474804</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.008334532615651091</v>
+        <v>0.1392592260546075</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.742365921837788</v>
+        <v>2.820920737901162</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.746690666044179</v>
+        <v>-4.462198309668542</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9576269131711688</v>
+        <v>1.071423855721423</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.008334532615651091</v>
+        <v>0.1392592260546075</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.861660323471979</v>
+        <v>2.940215139535352</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.760557427378097</v>
+        <v>-4.47606507100246</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.952913537623735</v>
+        <v>1.06671048017399</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.02952338411817185</v>
+        <v>0.1014013093207846</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.839778902417818</v>
+        <v>2.918333718481192</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.715753255838167</v>
+        <v>-4.43126089946253</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9768437366366329</v>
+        <v>1.090640679186888</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.02952338411817185</v>
+        <v>0.1014013093207846</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.845787432814744</v>
+        <v>2.924342248878118</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.568010285603164</v>
+        <v>-4.283517929227528</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9338911460078334</v>
+        <v>1.047688088558088</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.1382839731167113</v>
+        <v>0.2692086665556677</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.844422068432873</v>
+        <v>2.922976884496248</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.651831506877863</v>
+        <v>-4.367339150502226</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9031562790294352</v>
+        <v>1.01695322157969</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.1382839731167113</v>
+        <v>0.2692086665556677</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.847215689964354</v>
+        <v>2.925770506027729</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.645678800825078</v>
+        <v>-4.361186444449442</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9062797098422073</v>
+        <v>1.020076652392462</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.1444366791694956</v>
+        <v>0.275361372608452</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.851569661987683</v>
+        <v>2.930124478051057</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.66248809897558</v>
+        <v>-4.377995742599944</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8986364673221168</v>
+        <v>1.012433409872371</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.127627381018994</v>
+        <v>0.2585520744579504</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.840564559837493</v>
+        <v>2.919119375900867</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.600190100199458</v>
+        <v>-4.315697743823821</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9898912206293864</v>
+        <v>1.103688163179641</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.127627381018994</v>
+        <v>0.2585520744579504</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.906900113634314</v>
+        <v>2.985454929697688</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.3983999025343</v>
+        <v>-4.113907546158663</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8728993014095767</v>
+        <v>0.9866962439598315</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.3256455731881484</v>
+        <v>0.4565702666271048</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.828003030649934</v>
+        <v>2.906557846713307</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.449286615220495</v>
+        <v>-4.164794258844858</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9228348486572742</v>
+        <v>1.036631791207529</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.2747588605019538</v>
+        <v>0.4056835539409102</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.867761235360392</v>
+        <v>2.946316051423766</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.547027159845469</v>
+        <v>-4.262534803469832</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8983663669233279</v>
+        <v>1.012163309473583</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.2588695823689736</v>
+        <v>0.38979427580793</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.872855404596647</v>
+        <v>2.951410220660021</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.607236457850754</v>
+        <v>-4.322744101475117</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8728186285458857</v>
+        <v>0.9866155710961404</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.1986602843636891</v>
+        <v>0.3295849778026455</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.835265806618148</v>
+        <v>2.913820622681522</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.530814411418827</v>
+        <v>-4.372696693316962</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9018790651585848</v>
+        <v>0.9651261523993313</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.1986602843636891</v>
+        <v>0.3295849778026455</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.833757424658077</v>
+        <v>2.912312240721451</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.486441279780259</v>
+        <v>-4.328323561678393</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9194911852494485</v>
+        <v>0.982738272490195</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.2430334160022577</v>
+        <v>0.3739581094412141</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.860244171076654</v>
+        <v>2.938798987140028</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.508921630639144</v>
+        <v>-4.350803912537278</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9048928390444853</v>
+        <v>0.9681399262852315</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.2430334160022577</v>
+        <v>0.3739581094412141</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.854637965215245</v>
+        <v>2.933192781278619</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.461265900078088</v>
+        <v>-4.303148181976222</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9303368882967122</v>
+        <v>0.9935839755374585</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.2906891465633133</v>
+        <v>0.4216138400022698</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.889613160579683</v>
+        <v>2.968167976643056</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.360747741579333</v>
+        <v>-4.202630023477467</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9754365250709389</v>
+        <v>1.038683612311685</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.3912073050620679</v>
+        <v>0.5221319985010243</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.95481642905366</v>
+        <v>3.033371245117034</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.421414331981723</v>
+        <v>-4.263296613879856</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9379245613858553</v>
+        <v>1.001171648626602</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.3095089883435342</v>
+        <v>0.4404336817824906</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.892552111498413</v>
+        <v>2.971106927561786</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.376575930373324</v>
+        <v>-4.218458212271457</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9599576246398431</v>
+        <v>1.02320471188059</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.3140524212884037</v>
+        <v>0.4449771147273601</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.899375873875963</v>
+        <v>2.977930689939337</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.396074386615332</v>
+        <v>-4.237956668513466</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9563191817741179</v>
+        <v>1.019566269014865</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.2659677800084994</v>
+        <v>0.3968924734474558</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.874686028739098</v>
+        <v>2.953240844802472</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.351871549529432</v>
+        <v>-4.193753831427565</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9798799191363152</v>
+        <v>1.043127006377062</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.3101706170943999</v>
+        <v>0.4410953105333563</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.907087333518475</v>
+        <v>2.985642149581849</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.388850577192875</v>
+        <v>-4.230732859091008</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9634983085401858</v>
+        <v>1.026745395780932</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.3471445188857304</v>
+        <v>0.4780692123246868</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.927681675062521</v>
+        <v>3.006236491125895</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.230559159653603</v>
+        <v>-4.072441441551736</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.078062640738934</v>
+        <v>1.141309727979681</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.3471445188857304</v>
+        <v>0.4780692123246868</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.978929440245561</v>
+        <v>3.057484256308935</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.022917156019126</v>
+        <v>-3.86479943791726</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.159560146786978</v>
+        <v>1.222807234027724</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.5547865225202065</v>
+        <v>0.685711215959163</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.1019553470205</v>
+        <v>3.180510163083873</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.971885063296598</v>
+        <v>-3.813767345194732</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.174921212114259</v>
+        <v>1.238168299355006</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.6058186152427345</v>
+        <v>0.7367433086816909</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.127522830892286</v>
+        <v>3.20607764695566</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.906660882169392</v>
+        <v>-3.748543164067526</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.218198288657846</v>
+        <v>1.281445375898593</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.6710427963699401</v>
+        <v>0.8019674898088965</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.183844743661315</v>
+        <v>3.262399559724689</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.869233862098258</v>
+        <v>-3.711116143996393</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.22913006898558</v>
+        <v>1.292377156226327</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.6762943343991218</v>
+        <v>0.8072190278380782</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.182956638778104</v>
+        <v>3.261511454841478</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.889345518132967</v>
+        <v>-3.731227800031101</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.222342198902937</v>
+        <v>1.285589286143684</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.687321679396541</v>
+        <v>0.8182463728354974</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.190829838107796</v>
+        <v>3.26938465417117</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.835600703705762</v>
+        <v>-3.677482985603896</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.40439789569503</v>
+        <v>1.467644982935776</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.697384988837003</v>
+        <v>0.8283096822759594</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.357425594793284</v>
+        <v>3.435980410856658</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.760818442680749</v>
+        <v>-3.602700724578884</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.554423709322852</v>
+        <v>1.617670796563599</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.7721672498620156</v>
+        <v>0.903091943300972</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.522407860626109</v>
+        <v>3.600962676689483</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.734734358416941</v>
+        <v>-3.576616640315076</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.556565319042234</v>
+        <v>1.619812406282981</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.7721672498620156</v>
+        <v>0.903091943300972</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.514115836639968</v>
+        <v>3.592670652703342</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.656603177567995</v>
+        <v>-3.498485459466129</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.586010986965593</v>
+        <v>1.649258074206339</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.8463440607457001</v>
+        <v>0.9772687541846565</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.556815118753958</v>
+        <v>3.635369934817332</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.647710716174712</v>
+        <v>-3.489592998072846</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.607122377249697</v>
+        <v>1.670369464490443</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.8463440607457001</v>
+        <v>0.9772687541846565</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.574369524480749</v>
+        <v>3.652924340544123</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.816186833144589</v>
+        <v>-3.658069115042724</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.53158697786633</v>
+        <v>1.594834065107076</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.8183962250291194</v>
+        <v>0.9493209184680758</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.549455870455385</v>
+        <v>3.628010686518759</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.118387304283006</v>
+        <v>-2.96026958618114</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.791976486598825</v>
+        <v>1.855223573839571</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.7480481656587086</v>
+        <v>0.8789728590976651</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.488516732021</v>
+        <v>3.567071548084374</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.095666200599854</v>
+        <v>-2.937548482497988</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.791728950568991</v>
+        <v>1.854976037809737</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.7480481656587086</v>
+        <v>0.8789728590976651</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.479180754517905</v>
+        <v>3.557735570581279</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.224868013893896</v>
+        <v>-3.06675029579203</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.898954351102543</v>
+        <v>1.962201438343289</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.6188463523646663</v>
+        <v>0.7497710458036229</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.560565792392648</v>
+        <v>3.639120608456023</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.379649020672152</v>
+        <v>-3.221531302570286</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.874119770884887</v>
+        <v>1.937366858125634</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.5854786783101902</v>
+        <v>0.7164033717491467</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.57762301045361</v>
+        <v>3.656177826516983</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.372594330456978</v>
+        <v>-3.214476612355112</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.873617002960501</v>
+        <v>1.936864090201248</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.592533368525364</v>
+        <v>0.7234580619643205</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.578531180572259</v>
+        <v>3.657085996635633</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.34564310613049</v>
+        <v>-3.187525388028624</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.894403646335838</v>
+        <v>1.957650733576584</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.6074137145530831</v>
+        <v>0.7383384079920396</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.597465541833632</v>
+        <v>3.676020357897006</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.481596114186806</v>
+        <v>-3.323478396084941</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.024125575258272</v>
+        <v>2.087372662499018</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.6074137145530831</v>
+        <v>0.7383384079920396</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.781568673978592</v>
+        <v>3.860123490041965</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.504004231991678</v>
+        <v>-3.345886513889813</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.007279023039316</v>
+        <v>2.070526110280063</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.6074137145530831</v>
+        <v>0.7383384079920396</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.773685368881585</v>
+        <v>3.852240184944959</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.652009999471078</v>
+        <v>-3.493892281369212</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.950130715597194</v>
+        <v>2.01337780283794</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.5206867056895417</v>
+        <v>0.6516113991284982</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.723703163113097</v>
+        <v>3.802257979176471</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.661450925359608</v>
+        <v>-3.503333207257742</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.002608062963628</v>
+        <v>2.065855150204375</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.6431138232329331</v>
+        <v>0.7740385166718896</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.853413151360979</v>
+        <v>3.931967967424353</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.713724532695249</v>
+        <v>-3.555606814593383</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.984589714574673</v>
+        <v>2.04783680181542</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.5908402158972919</v>
+        <v>0.7217649093362484</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.824940081504896</v>
+        <v>3.903494897568269</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.790054510296155</v>
+        <v>-3.631936792194289</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.952169536428086</v>
+        <v>2.015416623668832</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.5908402158972919</v>
+        <v>0.7217649093362484</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.823051894398671</v>
+        <v>3.901606710462044</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887744</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.992308230620508</v>
+        <v>-3.834190512518643</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.866088277901207</v>
+        <v>1.929335365141953</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.3885864955729384</v>
+        <v>0.5195111890118949</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.696519891806921</v>
+        <v>3.775074707870295</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-4.153876656147763</v>
+        <v>-3.995758938045898</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.799894917900457</v>
+        <v>1.863142005141203</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.261803571775059</v>
+        <v>0.3927282652140155</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.618884147738346</v>
+        <v>3.697438963801719</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647101</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.286177948245316</v>
+        <v>-4.128060230143451</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.760047807927354</v>
+        <v>1.823294895168101</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.261803571775059</v>
+        <v>0.3927282652140155</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.631957554604264</v>
+        <v>3.710512370667638</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.749896851763529</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.287739591060176</v>
+        <v>-4.129621872958311</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.759423150801411</v>
+        <v>1.822670238042157</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.261803571775059</v>
+        <v>0.3927282652140155</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.631957554604264</v>
+        <v>3.710512370667638</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392112</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.315640378169649</v>
+        <v>-4.157522660067784</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.746786877084624</v>
+        <v>1.81003396432537</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.2272066476321242</v>
+        <v>0.3581313410710807</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.609723441245505</v>
+        <v>3.688278257308879</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172523</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.438166480872543</v>
+        <v>-4.280048762770678</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.694540879980665</v>
+        <v>1.757787967221411</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.1046805449292303</v>
+        <v>0.2356052383681868</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.532972223600968</v>
+        <v>3.611527039664342</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971074</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.668680977058131</v>
+        <v>-4.510563258956267</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.669041041096933</v>
+        <v>1.732288128337679</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.1258339512563584</v>
+        <v>0.005090742182598085</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.461369485480118</v>
+        <v>3.539924301543492</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199802</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.925401795052956</v>
+        <v>-4.767284076951091</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.70666443290085</v>
+        <v>1.769911520141596</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.2342485254001732</v>
+        <v>-0.1033238319612167</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.536632459995676</v>
+        <v>3.61518727605905</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622232</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-5.079388212829096</v>
+        <v>-4.921270494727231</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.714050134936034</v>
+        <v>1.77729722217678</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.2342485254001732</v>
+        <v>-0.1033238319612167</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.605612729141316</v>
+        <v>3.68416754520469</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808524</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-5.028866309001431</v>
+        <v>-4.870748590899566</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.720310098587221</v>
+        <v>1.783557185827967</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.2342485254001732</v>
+        <v>-0.1033238319612167</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.591663931261437</v>
+        <v>3.670218747324811</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.65634689399489</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.281341463009155</v>
+        <v>-5.12322374490729</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.631190526039545</v>
+        <v>1.694437613280291</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.2342485254001732</v>
+        <v>-0.1033238319612167</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.603534420316851</v>
+        <v>3.682089236380225</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358294</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.550814264930863</v>
+        <v>-5.392696546828998</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.524611939789806</v>
+        <v>1.587859027030552</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.2342485254001732</v>
+        <v>-0.1033238319612167</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.604744954835795</v>
+        <v>3.683299770899168</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637086</v>
+        <v>3.663523617637083</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.708358336660305</v>
+        <v>-5.55024061855844</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.465716053325351</v>
+        <v>1.528963140566097</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.3011503305404477</v>
+        <v>-0.1702256371014912</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.568725613978951</v>
+        <v>3.647280430042325</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301342</v>
+        <v>3.65216331330134</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.986322732243578</v>
+        <v>-5.828205014141713</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.34960814782823</v>
+        <v>1.412855235068977</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.390770064825932</v>
+        <v>-0.2598453713869755</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.51003162614385</v>
+        <v>3.588586442207224</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215465</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-6.208853518922301</v>
+        <v>-5.945172706780604</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.422799889855785</v>
+        <v>1.528272214712465</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.390770064825932</v>
+        <v>-0.2598453713869755</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.672235682842894</v>
+        <v>3.750790498906268</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456691</v>
+        <v>3.696553628456688</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.293571461143254</v>
+        <v>-6.088958510736231</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.383759350931218</v>
+        <v>1.465604531094028</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.4758860937539783</v>
+        <v>-0.3392434228045256</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.616012703449881</v>
+        <v>3.697998306019552</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253287</v>
+        <v>3.750058176253283</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.375506279412138</v>
+        <v>-6.170893329005114</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.361214841192156</v>
+        <v>1.443060021354965</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.4858208393410585</v>
+        <v>-0.3491781683916058</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.620281273666124</v>
+        <v>3.702266876235795</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717831</v>
+        <v>3.783647027717827</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.321768106011875</v>
+        <v>-6.117155155604852</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.391635749008163</v>
+        <v>1.473480929170973</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4320826659407964</v>
+        <v>-0.2954399949913437</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.661449816162183</v>
+        <v>3.743435418731855</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616947</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.211761822534654</v>
+        <v>-6.00714887212763</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.427791149643228</v>
+        <v>1.509636329806037</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.4088780940235212</v>
+        <v>-0.2722354230740684</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.667525446556724</v>
+        <v>3.749511049126395</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203661</v>
+        <v>3.785578085203659</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.068702246793729</v>
+        <v>-5.864089296386705</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.489264990661572</v>
+        <v>1.571110170824381</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.4008646674335419</v>
+        <v>-0.2642219964840892</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.676583513232686</v>
+        <v>3.758569115802358</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436927</v>
+        <v>3.777251572436925</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.767255521321891</v>
+        <v>-5.562642570914868</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.617104563732843</v>
+        <v>1.698949743895652</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.09941794196170467</v>
+        <v>0.03722472898774809</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.864712431398324</v>
+        <v>3.946698033967996</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064765</v>
+        <v>3.812650101064763</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.791845765557075</v>
+        <v>-5.587232815150052</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.608239643791479</v>
+        <v>1.690084823954289</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.09941794196170467</v>
+        <v>0.03722472898774809</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.865683609151034</v>
+        <v>3.947669211720706</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859299</v>
+        <v>3.821198342859297</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.740807389550555</v>
+        <v>-5.536194439143531</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.629497898573843</v>
+        <v>1.711343078736653</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.09941794196170467</v>
+        <v>0.03722472898774809</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.86652651353079</v>
+        <v>3.948512116100462</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354684</v>
+        <v>3.831748677354682</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.699668094683924</v>
+        <v>-5.4950551442769</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.664991715394641</v>
+        <v>1.74683689555745</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.05827864709507385</v>
+        <v>0.07836402385437891</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.910248189324914</v>
+        <v>3.992233791894585</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085619</v>
+        <v>3.825767093085617</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.589061954604322</v>
+        <v>-5.384449004197299</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.525418167550416</v>
+        <v>1.607263347713226</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.05232749298452816</v>
+        <v>0.1889701639339809</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.79279586949661</v>
+        <v>3.874781472066281</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462781</v>
+        <v>3.804703121462778</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.719642689135164</v>
+        <v>-5.397059348154146</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.476687917812043</v>
+        <v>1.60572125420445</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.07825324154631436</v>
+        <v>0.1763598199771336</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.717949472852068</v>
+        <v>3.870717309766137</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218599</v>
+        <v>3.775043021218595</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.555146354944203</v>
+        <v>-5.232563013963184</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.52691327056451</v>
+        <v>1.655946606956918</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.07825324154631436</v>
+        <v>0.1763598199771336</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.70237629192815</v>
+        <v>3.855144128842219</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462768</v>
+        <v>3.821044820462765</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.430665874220251</v>
+        <v>-5.108082533239233</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.575893173290521</v>
+        <v>1.704926509682928</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.07825324154631436</v>
+        <v>0.1763598199771336</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.70156400236458</v>
+        <v>3.854331839278649</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533049</v>
+        <v>3.832321184533047</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.441051069110141</v>
+        <v>-5.118467728129122</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.581607874459637</v>
+        <v>1.710641210852045</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.08863843643620367</v>
+        <v>0.1659746250872443</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.705201664555719</v>
+        <v>3.857969501469788</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834429654120418</v>
+        <v>3.834429654120417</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.350296593081499</v>
+        <v>-5.02771325210048</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.688746670647519</v>
+        <v>1.817780007039926</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.002116039592438057</v>
+        <v>0.256729101115886</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.830491355949329</v>
+        <v>3.983259192863398</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.762794790075265</v>
+        <v>3.790765701281381</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.73328674058193</v>
+        <v>3.780671978392915</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.350296593081499</v>
+        <v>-5.02771325210048</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.688746670647519</v>
+        <v>1.817780007039926</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.002116039592438057</v>
+        <v>0.256729101115886</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.726350537568297</v>
+        <v>3.773735775379282</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240728.xlsx
+++ b/tame_output/ON/bt/strategyON_20240728.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-80.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.2%</t>
+          <t>111.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.7%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.1%</t>
+          <t>-45.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.9%</t>
+          <t>454.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-664.3%</t>
+          <t>-684.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,42 +1140,42 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24649.8%</t>
+          <t>-24644.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-194.4%</t>
+          <t>-212.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-123.1%</t>
+          <t>-135.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-198.3%</t>
+          <t>-225.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-68.7%</t>
+          <t>-74.1%</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
@@ -46976,10 +46976,10 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.372696693316962</v>
+        <v>-4.361858294396</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9651261523993313</v>
+        <v>0.9694615119677159</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3295849778026455</v>
@@ -46999,10 +46999,10 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.328323561678393</v>
+        <v>-4.317485162757431</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.982738272490195</v>
+        <v>0.9870736320585796</v>
       </c>
       <c r="F1976" t="n">
         <v>0.3739581094412141</v>
@@ -47022,10 +47022,10 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.350803912537278</v>
+        <v>-4.339965513616316</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9681399262852315</v>
+        <v>0.9724752858536161</v>
       </c>
       <c r="F1977" t="n">
         <v>0.3739581094412141</v>
@@ -47045,10 +47045,10 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.303148181976222</v>
+        <v>-4.29230978305526</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9935839755374585</v>
+        <v>0.9979193351058431</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4216138400022698</v>
@@ -47068,10 +47068,10 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.202630023477467</v>
+        <v>-4.191791624556505</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.038683612311685</v>
+        <v>1.04301897188007</v>
       </c>
       <c r="F1979" t="n">
         <v>0.5221319985010243</v>
@@ -47091,10 +47091,10 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.263296613879856</v>
+        <v>-4.252458214958894</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.001171648626602</v>
+        <v>1.005507008194987</v>
       </c>
       <c r="F1980" t="n">
         <v>0.4404336817824906</v>
@@ -47114,10 +47114,10 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.218458212271457</v>
+        <v>-4.207619813350496</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.02320471188059</v>
+        <v>1.027540071448975</v>
       </c>
       <c r="F1981" t="n">
         <v>0.4449771147273601</v>
@@ -47137,10 +47137,10 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.237956668513466</v>
+        <v>-4.227118269592504</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.019566269014865</v>
+        <v>1.023901628583249</v>
       </c>
       <c r="F1982" t="n">
         <v>0.3968924734474558</v>
@@ -47160,10 +47160,10 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.193753831427565</v>
+        <v>-4.182915432506603</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.043127006377062</v>
+        <v>1.047462365945447</v>
       </c>
       <c r="F1983" t="n">
         <v>0.4410953105333563</v>
@@ -47183,10 +47183,10 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.230732859091008</v>
+        <v>-4.219894460170046</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.026745395780932</v>
+        <v>1.031080755349317</v>
       </c>
       <c r="F1984" t="n">
         <v>0.4780692123246868</v>
@@ -47206,10 +47206,10 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.072441441551736</v>
+        <v>-4.061603042630774</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.141309727979681</v>
+        <v>1.145645087548065</v>
       </c>
       <c r="F1985" t="n">
         <v>0.4780692123246868</v>
@@ -47229,10 +47229,10 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.86479943791726</v>
+        <v>-3.853961038996298</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.222807234027724</v>
+        <v>1.227142593596109</v>
       </c>
       <c r="F1986" t="n">
         <v>0.685711215959163</v>
@@ -47252,10 +47252,10 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.813767345194732</v>
+        <v>-3.80292894627377</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.238168299355006</v>
+        <v>1.24250365892339</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7367433086816909</v>
@@ -47275,10 +47275,10 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.748543164067526</v>
+        <v>-3.737704765146565</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.281445375898593</v>
+        <v>1.285780735466977</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8019674898088965</v>
@@ -47298,10 +47298,10 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.711116143996393</v>
+        <v>-3.700277745075431</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.292377156226327</v>
+        <v>1.296712515794711</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8072190278380782</v>
@@ -47321,10 +47321,10 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.731227800031101</v>
+        <v>-3.720389401110139</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.285589286143684</v>
+        <v>1.289924645712068</v>
       </c>
       <c r="F1990" t="n">
         <v>0.8182463728354974</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.677482985603896</v>
+        <v>-3.666644586682934</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.467644982935776</v>
+        <v>1.471980342504161</v>
       </c>
       <c r="F1991" t="n">
         <v>0.8283096822759594</v>
@@ -47367,10 +47367,10 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.602700724578884</v>
+        <v>-3.591862325657922</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.617670796563599</v>
+        <v>1.622006156131983</v>
       </c>
       <c r="F1992" t="n">
         <v>0.903091943300972</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.576616640315076</v>
+        <v>-3.565778241394114</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.619812406282981</v>
+        <v>1.624147765851365</v>
       </c>
       <c r="F1993" t="n">
         <v>0.903091943300972</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.498485459466129</v>
+        <v>-3.487647060545167</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.649258074206339</v>
+        <v>1.653593433774724</v>
       </c>
       <c r="F1994" t="n">
         <v>0.9772687541846565</v>
@@ -47436,10 +47436,10 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.489592998072846</v>
+        <v>-3.478754599151884</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.670369464490443</v>
+        <v>1.674704824058828</v>
       </c>
       <c r="F1995" t="n">
         <v>0.9772687541846565</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.658069115042724</v>
+        <v>-3.647230716121762</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.594834065107076</v>
+        <v>1.599169424675461</v>
       </c>
       <c r="F1996" t="n">
         <v>0.9493209184680758</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.96026958618114</v>
+        <v>-2.949431187260179</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.855223573839571</v>
+        <v>1.859558933407956</v>
       </c>
       <c r="F1997" t="n">
         <v>0.8789728590976651</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.937548482497988</v>
+        <v>-2.926710083577026</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.854976037809737</v>
+        <v>1.859311397378122</v>
       </c>
       <c r="F1998" t="n">
         <v>0.8789728590976651</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.06675029579203</v>
+        <v>-3.055911896871069</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.962201438343289</v>
+        <v>1.966536797911674</v>
       </c>
       <c r="F1999" t="n">
         <v>0.7497710458036229</v>
@@ -47551,10 +47551,10 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.221531302570286</v>
+        <v>-3.210692903649324</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.937366858125634</v>
+        <v>1.941702217694018</v>
       </c>
       <c r="F2000" t="n">
         <v>0.7164033717491467</v>
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.214476612355112</v>
+        <v>-3.345781318121344</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.936864090201248</v>
+        <v>1.884342207894755</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7234580619643205</v>
+        <v>0.5813149572771273</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.657085996635633</v>
+        <v>3.571800133823317</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.187525388028624</v>
+        <v>-3.318830093794856</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.957650733576584</v>
+        <v>1.905128851270092</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7383384079920396</v>
+        <v>0.5961953033048465</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.676020357897006</v>
+        <v>3.59073449508469</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.323478396084941</v>
+        <v>-3.454783101851172</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.087372662499018</v>
+        <v>2.034850780192525</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7383384079920396</v>
+        <v>0.5961953033048465</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.860123490041965</v>
+        <v>3.774837627229649</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.345886513889813</v>
+        <v>-3.477191219656044</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.070526110280063</v>
+        <v>2.01800422797357</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7383384079920396</v>
+        <v>0.5961953033048465</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.852240184944959</v>
+        <v>3.766954322132642</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.493892281369212</v>
+        <v>-3.625196987135443</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.01337780283794</v>
+        <v>1.960855920531447</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6516113991284982</v>
+        <v>0.509468294441305</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.802257979176471</v>
+        <v>3.716972116364155</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.503333207257742</v>
+        <v>-3.634637913023973</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.065855150204375</v>
+        <v>2.013333267897882</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7740385166718896</v>
+        <v>0.6318954119846965</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.931967967424353</v>
+        <v>3.846682104612037</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.555606814593383</v>
+        <v>-3.686911520359615</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.04783680181542</v>
+        <v>1.995314919508927</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7217649093362484</v>
+        <v>0.5796218046490552</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.903494897568269</v>
+        <v>3.818209034755953</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.631936792194289</v>
+        <v>-3.763241497960521</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.015416623668832</v>
+        <v>1.96289474136234</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7217649093362484</v>
+        <v>0.5796218046490552</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.901606710462044</v>
+        <v>3.816320847649728</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887744</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.834190512518643</v>
+        <v>-3.965495218284874</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.929335365141953</v>
+        <v>1.876813482835461</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5195111890118949</v>
+        <v>0.3773680843247018</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.775074707870295</v>
+        <v>3.689788845057979</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.995758938045898</v>
+        <v>-4.127063643812129</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.863142005141203</v>
+        <v>1.810620122834711</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3927282652140155</v>
+        <v>0.2505851605268224</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.697438963801719</v>
+        <v>3.612153100989404</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647101</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.128060230143451</v>
+        <v>-4.259364935909682</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.823294895168101</v>
+        <v>1.770773012861608</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3927282652140155</v>
+        <v>0.2505851605268224</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.710512370667638</v>
+        <v>3.625226507855322</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763529</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.129621872958311</v>
+        <v>-4.260926578724542</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.822670238042157</v>
+        <v>1.770148355735665</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3927282652140155</v>
+        <v>0.2505851605268224</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.710512370667638</v>
+        <v>3.625226507855322</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392112</v>
+        <v>3.715834055392114</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.157522660067784</v>
+        <v>-4.288827365834014</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.81003396432537</v>
+        <v>1.757512082018877</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3581313410710807</v>
+        <v>0.2159882363838876</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.688278257308879</v>
+        <v>3.602992394496563</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172523</v>
+        <v>3.684909939172525</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.280048762770678</v>
+        <v>-4.411353468536908</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.757787967221411</v>
+        <v>1.705266084914919</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2356052383681868</v>
+        <v>0.09346213368099371</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.611527039664342</v>
+        <v>3.526241176852026</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971074</v>
+        <v>3.619362241971076</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.510563258956267</v>
+        <v>-4.641867964722497</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.732288128337679</v>
+        <v>1.679766246031187</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.005090742182598085</v>
+        <v>-0.137052362504595</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.539924301543492</v>
+        <v>3.454638438731176</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199802</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.767284076951091</v>
+        <v>-4.89858878271732</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.769911520141596</v>
+        <v>1.717389637835105</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.2454669366484099</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.61518727605905</v>
+        <v>3.529901413246734</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622232</v>
+        <v>3.668303164622234</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.921270494727231</v>
+        <v>-5.052575200493461</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.77729722217678</v>
+        <v>1.724775339870288</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.2454669366484099</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.68416754520469</v>
+        <v>3.598881682392374</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808524</v>
+        <v>3.619937176808526</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.870748590899566</v>
+        <v>-5.002053296665795</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.783557185827967</v>
+        <v>1.731035303521475</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.2454669366484099</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.670218747324811</v>
+        <v>3.584932884512495</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.65634689399489</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.12322374490729</v>
+        <v>-5.254528450673519</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.694437613280291</v>
+        <v>1.6419157309738</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.2454669366484099</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.682089236380225</v>
+        <v>3.596803373567909</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358294</v>
+        <v>3.674042696358296</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.392696546828998</v>
+        <v>-5.524001252595228</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.587859027030552</v>
+        <v>1.53533714472406</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.2454669366484099</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.683299770899168</v>
+        <v>3.598013908086853</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637083</v>
+        <v>3.663523617637085</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.55024061855844</v>
+        <v>-5.681545324324669</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.528963140566097</v>
+        <v>1.476441258259605</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1702256371014912</v>
+        <v>-0.3123687417886843</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.647280430042325</v>
+        <v>3.56199456723001</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.65216331330134</v>
+        <v>3.652163313301342</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.828205014141713</v>
+        <v>-5.959509719907943</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.412855235068977</v>
+        <v>1.360333352762485</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2598453713869755</v>
+        <v>-0.4019884760741686</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.588586442207224</v>
+        <v>3.503300579394908</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215465</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.945172706780604</v>
+        <v>-6.076477412546834</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.528272214712465</v>
+        <v>1.475750332405973</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2598453713869755</v>
+        <v>-0.4019884760741686</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.750790498906268</v>
+        <v>3.665504636093952</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456688</v>
+        <v>3.69655362845669</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.088958510736231</v>
+        <v>-6.161195354767787</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.465604531094028</v>
+        <v>1.436709793481405</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.3392434228045256</v>
+        <v>-0.487104505002215</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.697998306019552</v>
+        <v>3.609281656700939</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253283</v>
+        <v>3.750058176253285</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.170893329005114</v>
+        <v>-6.309558086585883</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.443060021354965</v>
+        <v>1.387594118322658</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3491781683916058</v>
+        <v>-0.5656313798940531</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.702266876235795</v>
+        <v>3.572394949334327</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717827</v>
+        <v>3.783647027717829</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.117155155604852</v>
+        <v>-6.255819913185621</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.473480929170973</v>
+        <v>1.418015026138665</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2954399949913437</v>
+        <v>-0.511893206493791</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.743435418731855</v>
+        <v>3.613563491830387</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616945</v>
+        <v>3.798310944616946</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.00714887212763</v>
+        <v>-6.1458136297084</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.509636329806037</v>
+        <v>1.454170426773729</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2722354230740684</v>
+        <v>-0.4886886345765158</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.749511049126395</v>
+        <v>3.619639122224927</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203659</v>
+        <v>3.785578085203661</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.864089296386705</v>
+        <v>-6.002754053967474</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.571110170824381</v>
+        <v>1.515644267792074</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2642219964840892</v>
+        <v>-0.4806752079865365</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.758569115802358</v>
+        <v>3.628697188900889</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436925</v>
+        <v>3.777251572436927</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.562642570914868</v>
+        <v>-5.701307328495636</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.698949743895652</v>
+        <v>1.643483840863345</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.03722472898774809</v>
+        <v>-0.1792284825146992</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.946698033967996</v>
+        <v>3.816826107066527</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064763</v>
+        <v>3.812650101064765</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.587232815150052</v>
+        <v>-5.72589757273082</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.690084823954289</v>
+        <v>1.634618920921981</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.03722472898774809</v>
+        <v>-0.1792284825146992</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.947669211720706</v>
+        <v>3.817797284819238</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859297</v>
+        <v>3.821198342859299</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.536194439143531</v>
+        <v>-5.6748591967243</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.711343078736653</v>
+        <v>1.655877175704345</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.03722472898774809</v>
+        <v>-0.1792284825146992</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.948512116100462</v>
+        <v>3.818640189198993</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354682</v>
+        <v>3.831748677354684</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.4950551442769</v>
+        <v>-5.633719901857669</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.74683689555745</v>
+        <v>1.691370992525143</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.07836402385437891</v>
+        <v>-0.1380891876480684</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.992233791894585</v>
+        <v>3.862361864993117</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085617</v>
+        <v>3.825767093085619</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.384449004197299</v>
+        <v>-5.523113761778067</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.607263347713226</v>
+        <v>1.551797444680918</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1889701639339809</v>
+        <v>-0.02748304756846642</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.874781472066281</v>
+        <v>3.744909545164813</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462778</v>
+        <v>3.80470312146278</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.397059348154146</v>
+        <v>-5.653694496308909</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.60572125420445</v>
+        <v>1.503067194942545</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.1763598199771336</v>
+        <v>-0.1580637820993089</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.870717309766137</v>
+        <v>3.670063148520271</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218595</v>
+        <v>3.775043021218597</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.232563013963184</v>
+        <v>-5.489198162117948</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.655946606956918</v>
+        <v>1.553292547695012</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.1763598199771336</v>
+        <v>-0.1580637820993089</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.855144128842219</v>
+        <v>3.654489967596354</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462765</v>
+        <v>3.821044820462767</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.108082533239233</v>
+        <v>-5.364717681393996</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.704926509682928</v>
+        <v>1.602272450421023</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.1763598199771336</v>
+        <v>-0.1580637820993089</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.854331839278649</v>
+        <v>3.653677678032783</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533047</v>
+        <v>3.832321184533049</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.118467728129122</v>
+        <v>-5.375102876283886</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.710641210852045</v>
+        <v>1.607987151590139</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.1659746250872443</v>
+        <v>-0.1684489769891983</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.857969501469788</v>
+        <v>3.657315340223922</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834429654120417</v>
+        <v>3.834429654120422</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.02771325210048</v>
+        <v>-5.284348400255244</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.817780007039926</v>
+        <v>1.715125947778021</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.256729101115886</v>
+        <v>-0.07769450096055652</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.983259192863398</v>
+        <v>3.782605031617532</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.790765701281381</v>
+        <v>3.842771163672689</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.780671978392915</v>
+        <v>3.731243310712125</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.02771325210048</v>
+        <v>-5.225928722718818</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.817780007039926</v>
+        <v>1.640515397310851</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.256729101115886</v>
+        <v>-0.01927482342413112</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.773735775379282</v>
+        <v>3.719678416657647</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240728.xlsx
+++ b/tame_output/ON/bt/strategyON_20240728.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>44.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>84.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>71.0%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.4%</t>
+          <t>-80.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.2%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-45.8%</t>
+          <t>-47.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.1%</t>
+          <t>453.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-684.2%</t>
+          <t>-674.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24644.6%</t>
+          <t>-24649.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-212.2%</t>
+          <t>-198.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-135.1%</t>
+          <t>-132.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-225.9%</t>
+          <t>-212.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-56.6%</t>
         </is>
       </c>
     </row>
@@ -46976,10 +46976,10 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.361858294396</v>
+        <v>-4.246322055043191</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9694615119677159</v>
+        <v>1.01567600770884</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3295849778026455</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.317485162757431</v>
+        <v>-4.201948923404622</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9870736320585796</v>
+        <v>1.033288127799703</v>
       </c>
       <c r="F1976" t="n">
         <v>0.3739581094412141</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.339965513616316</v>
+        <v>-4.224429274263507</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9724752858536161</v>
+        <v>1.01868978159474</v>
       </c>
       <c r="F1977" t="n">
         <v>0.3739581094412141</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.29230978305526</v>
+        <v>-4.176773543702451</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9979193351058431</v>
+        <v>1.044133830846967</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4216138400022698</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.191791624556505</v>
+        <v>-4.076255385203696</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.04301897188007</v>
+        <v>1.089233467621193</v>
       </c>
       <c r="F1979" t="n">
         <v>0.5221319985010243</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.252458214958894</v>
+        <v>-4.136921975606086</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.005507008194987</v>
+        <v>1.05172150393611</v>
       </c>
       <c r="F1980" t="n">
         <v>0.4404336817824906</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.207619813350496</v>
+        <v>-4.092083573997687</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.027540071448975</v>
+        <v>1.073754567190098</v>
       </c>
       <c r="F1981" t="n">
         <v>0.4449771147273601</v>
@@ -47137,10 +47137,10 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.227118269592504</v>
+        <v>-4.111582030239695</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.023901628583249</v>
+        <v>1.070116124324373</v>
       </c>
       <c r="F1982" t="n">
         <v>0.3968924734474558</v>
@@ -47160,10 +47160,10 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.182915432506603</v>
+        <v>-4.067379193153795</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.047462365945447</v>
+        <v>1.09367686168657</v>
       </c>
       <c r="F1983" t="n">
         <v>0.4410953105333563</v>
@@ -47183,10 +47183,10 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.219894460170046</v>
+        <v>-4.104358220817238</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.031080755349317</v>
+        <v>1.07729525109044</v>
       </c>
       <c r="F1984" t="n">
         <v>0.4780692123246868</v>
@@ -47206,10 +47206,10 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.061603042630774</v>
+        <v>-3.946066803277966</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.145645087548065</v>
+        <v>1.191859583289189</v>
       </c>
       <c r="F1985" t="n">
         <v>0.4780692123246868</v>
@@ -47229,10 +47229,10 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.853961038996298</v>
+        <v>-3.738424799643489</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.227142593596109</v>
+        <v>1.273357089337233</v>
       </c>
       <c r="F1986" t="n">
         <v>0.685711215959163</v>
@@ -47252,10 +47252,10 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.80292894627377</v>
+        <v>-3.687392706920961</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.24250365892339</v>
+        <v>1.288718154664514</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7367433086816909</v>
@@ -47275,10 +47275,10 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.737704765146565</v>
+        <v>-3.622168525793755</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.285780735466977</v>
+        <v>1.331995231208101</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8019674898088965</v>
@@ -47298,10 +47298,10 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.700277745075431</v>
+        <v>-3.584741505722622</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.296712515794711</v>
+        <v>1.342927011535835</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8072190278380782</v>
@@ -47321,10 +47321,10 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.720389401110139</v>
+        <v>-3.60485316175733</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.289924645712068</v>
+        <v>1.336139141453192</v>
       </c>
       <c r="F1990" t="n">
         <v>0.8182463728354974</v>
@@ -47344,10 +47344,10 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.666644586682934</v>
+        <v>-3.551108347330125</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.471980342504161</v>
+        <v>1.518194838245285</v>
       </c>
       <c r="F1991" t="n">
         <v>0.8283096822759594</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.591862325657922</v>
+        <v>-3.476326086305113</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.622006156131983</v>
+        <v>1.668220651873107</v>
       </c>
       <c r="F1992" t="n">
         <v>0.903091943300972</v>
@@ -47390,10 +47390,10 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.565778241394114</v>
+        <v>-3.450242002041305</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.624147765851365</v>
+        <v>1.670362261592489</v>
       </c>
       <c r="F1993" t="n">
         <v>0.903091943300972</v>
@@ -47413,10 +47413,10 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.487647060545167</v>
+        <v>-3.372110821192358</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.653593433774724</v>
+        <v>1.699807929515847</v>
       </c>
       <c r="F1994" t="n">
         <v>0.9772687541846565</v>
@@ -47436,10 +47436,10 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.478754599151884</v>
+        <v>-3.363218359799075</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.674704824058828</v>
+        <v>1.720919319799952</v>
       </c>
       <c r="F1995" t="n">
         <v>0.9772687541846565</v>
@@ -47459,10 +47459,10 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.647230716121762</v>
+        <v>-3.531694476768953</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.599169424675461</v>
+        <v>1.645383920416585</v>
       </c>
       <c r="F1996" t="n">
         <v>0.9493209184680758</v>
@@ -47482,10 +47482,10 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.949431187260179</v>
+        <v>-2.833894947907369</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.859558933407956</v>
+        <v>1.90577342914908</v>
       </c>
       <c r="F1997" t="n">
         <v>0.8789728590976651</v>
@@ -47505,10 +47505,10 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.926710083577026</v>
+        <v>-2.811173844224217</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.859311397378122</v>
+        <v>1.905525893119245</v>
       </c>
       <c r="F1998" t="n">
         <v>0.8789728590976651</v>
@@ -47528,10 +47528,10 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.055911896871069</v>
+        <v>-2.940375657518259</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.966536797911674</v>
+        <v>2.012751293652797</v>
       </c>
       <c r="F1999" t="n">
         <v>0.7497710458036229</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.210692903649324</v>
+        <v>-3.095156664296515</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.941702217694018</v>
+        <v>1.987916713435141</v>
       </c>
       <c r="F2000" t="n">
         <v>0.7164033717491467</v>
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.345781318121344</v>
+        <v>-3.088101974081341</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.884342207894755</v>
+        <v>1.987413945510756</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.5813149572771273</v>
+        <v>0.7234580619643205</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.571800133823317</v>
+        <v>3.657085996635633</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.318830093794856</v>
+        <v>-3.061150749754853</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.905128851270092</v>
+        <v>2.008200588886093</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.5961953033048465</v>
+        <v>0.7383384079920396</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.59073449508469</v>
+        <v>3.676020357897006</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.454783101851172</v>
+        <v>-3.19710375781117</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.034850780192525</v>
+        <v>2.137922517808526</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.5961953033048465</v>
+        <v>0.7383384079920396</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.774837627229649</v>
+        <v>3.860123490041965</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.477191219656044</v>
+        <v>-3.219511875616042</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.01800422797357</v>
+        <v>2.12107596558957</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.5961953033048465</v>
+        <v>0.7383384079920396</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.766954322132642</v>
+        <v>3.852240184944959</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.625196987135443</v>
+        <v>-3.367517643095441</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.960855920531447</v>
+        <v>2.063927658147448</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.509468294441305</v>
+        <v>0.6516113991284982</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.716972116364155</v>
+        <v>3.802257979176471</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.634637913023973</v>
+        <v>-3.376958568983971</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.013333267897882</v>
+        <v>2.116405005513883</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.6318954119846965</v>
+        <v>0.7740385166718896</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.846682104612037</v>
+        <v>3.931967967424353</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.686911520359615</v>
+        <v>-3.571268457595885</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.995314919508927</v>
+        <v>2.041572144614419</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.5796218046490552</v>
+        <v>0.5797286280599759</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.818209034755953</v>
+        <v>3.818273128802506</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.763241497960521</v>
+        <v>-3.647598435196791</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.96289474136234</v>
+        <v>2.009151966467832</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.5796218046490552</v>
+        <v>0.5797286280599759</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.816320847649728</v>
+        <v>3.816384941696281</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.965495218284874</v>
+        <v>-3.849852155521144</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.876813482835461</v>
+        <v>1.923070707940953</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.3773680843247018</v>
+        <v>0.3774749077356225</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.689788845057979</v>
+        <v>3.689852939104531</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-4.127063643812129</v>
+        <v>-4.011420581048399</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.810620122834711</v>
+        <v>1.856877347940203</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.2505851605268224</v>
+        <v>0.2506919839377431</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.612153100989404</v>
+        <v>3.612217195035956</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.259364935909682</v>
+        <v>-4.143721873145952</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.770773012861608</v>
+        <v>1.8170302379671</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.2505851605268224</v>
+        <v>0.2506919839377431</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.625226507855322</v>
+        <v>3.625290601901875</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.260926578724542</v>
+        <v>-4.145283515960812</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.770148355735665</v>
+        <v>1.816405580841156</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.2505851605268224</v>
+        <v>0.2506919839377431</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.625226507855322</v>
+        <v>3.625290601901875</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392114</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.288827365834014</v>
+        <v>-4.173184303070284</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.757512082018877</v>
+        <v>1.803769307124369</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.2159882363838876</v>
+        <v>0.2160950597948083</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.602992394496563</v>
+        <v>3.603056488543116</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172525</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.411353468536908</v>
+        <v>-4.295710405773178</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.705266084914919</v>
+        <v>1.751523310020411</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.09346213368099371</v>
+        <v>0.09356895709191443</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.526241176852026</v>
+        <v>3.526305270898578</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971076</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.641867964722497</v>
+        <v>-4.526224901958767</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.679766246031187</v>
+        <v>1.726023471136679</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.137052362504595</v>
+        <v>-0.1369455390936743</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.454638438731176</v>
+        <v>3.454702532777729</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.89858878271732</v>
+        <v>-4.782945719953592</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.717389637835105</v>
+        <v>1.763646862940596</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.2454669366484099</v>
+        <v>-0.2453601132374891</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.529901413246734</v>
+        <v>3.529965507293287</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622234</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-5.052575200493461</v>
+        <v>-4.936932137729732</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.724775339870288</v>
+        <v>1.77103256497578</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.2454669366484099</v>
+        <v>-0.2453601132374891</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.598881682392374</v>
+        <v>3.598945776438927</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808526</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-5.002053296665795</v>
+        <v>-4.886410233902066</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.731035303521475</v>
+        <v>1.777292528626967</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.2454669366484099</v>
+        <v>-0.2453601132374891</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.584932884512495</v>
+        <v>3.584996978559047</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.254528450673519</v>
+        <v>-5.138885387909791</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.6419157309738</v>
+        <v>1.688172956079291</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.2454669366484099</v>
+        <v>-0.2453601132374891</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.596803373567909</v>
+        <v>3.596867467614461</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.524001252595228</v>
+        <v>-5.408358189831499</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.53533714472406</v>
+        <v>1.581594369829551</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.2454669366484099</v>
+        <v>-0.2453601132374891</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.598013908086853</v>
+        <v>3.598078002133405</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637085</v>
+        <v>3.663523617637086</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.681545324324669</v>
+        <v>-5.56590226156094</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.476441258259605</v>
+        <v>1.522698483365097</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.3123687417886843</v>
+        <v>-0.3122619183777636</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.56199456723001</v>
+        <v>3.562058661276562</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.959509719907943</v>
+        <v>-5.843866657144214</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.360333352762485</v>
+        <v>1.406590577867976</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.4019884760741686</v>
+        <v>-0.4018816526632479</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.503300579394908</v>
+        <v>3.503364673441461</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-6.076477412546834</v>
+        <v>-5.960834349783105</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.475750332405973</v>
+        <v>1.522007557511464</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.4019884760741686</v>
+        <v>-0.4018816526632479</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.665504636093952</v>
+        <v>3.665568730140505</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69655362845669</v>
+        <v>3.696553628456691</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.161195354767787</v>
+        <v>-6.045552292004058</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.436709793481405</v>
+        <v>1.482967018586897</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.487104505002215</v>
+        <v>-0.4869976815912943</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.609281656700939</v>
+        <v>3.609345750747491</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253285</v>
+        <v>3.750058176253287</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.309558086585883</v>
+        <v>-6.127487110272941</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.387594118322658</v>
+        <v>1.460422508847835</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.5656313798940531</v>
+        <v>-0.4969324271783744</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.572394949334327</v>
+        <v>3.613614320963734</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717829</v>
+        <v>3.783647027717831</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.255819913185621</v>
+        <v>-6.073748936872679</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.418015026138665</v>
+        <v>1.490843416663842</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.511893206493791</v>
+        <v>-0.4431942537781123</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.613563491830387</v>
+        <v>3.654782863459794</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616946</v>
+        <v>3.798310944616948</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.1458136297084</v>
+        <v>-5.963742653395458</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.454170426773729</v>
+        <v>1.526998817298906</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.4886886345765158</v>
+        <v>-0.4199896818608371</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.619639122224927</v>
+        <v>3.660858493854334</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203661</v>
+        <v>3.785578085203662</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.002754053967474</v>
+        <v>-5.820683077654532</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.515644267792074</v>
+        <v>1.58847265831725</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.4806752079865365</v>
+        <v>-0.4119762552708578</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.628697188900889</v>
+        <v>3.669916560530296</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436927</v>
+        <v>3.777251572436928</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.701307328495636</v>
+        <v>-5.519236352182695</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.643483840863345</v>
+        <v>1.716312231388522</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.1792284825146992</v>
+        <v>-0.1105295297990206</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.816826107066527</v>
+        <v>3.858045478695935</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.72589757273082</v>
+        <v>-5.543826596417879</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.634618920921981</v>
+        <v>1.707447311447158</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.1792284825146992</v>
+        <v>-0.1105295297990206</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.817797284819238</v>
+        <v>3.859016656448645</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.6748591967243</v>
+        <v>-5.492788220411359</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.655877175704345</v>
+        <v>1.728705566229522</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.1792284825146992</v>
+        <v>-0.1105295297990206</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.818640189198993</v>
+        <v>3.8598595608284</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.633719901857669</v>
+        <v>-5.451648925544728</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.691370992525143</v>
+        <v>1.76419938305032</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.1380891876480684</v>
+        <v>-0.06939023493238977</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.862361864993117</v>
+        <v>3.903581236622524</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.523113761778067</v>
+        <v>-5.341042785465126</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.551797444680918</v>
+        <v>1.624625835206095</v>
       </c>
       <c r="F2033" t="n">
-        <v>-0.02748304756846642</v>
+        <v>0.04121590514721224</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.744909545164813</v>
+        <v>3.78612891679422</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80470312146278</v>
+        <v>3.804703121462781</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.653694496308909</v>
+        <v>-5.471623519995968</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.503067194942545</v>
+        <v>1.575895585467721</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.1580637820993089</v>
+        <v>-0.08936482938363027</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.670063148520271</v>
+        <v>3.711282520149678</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218597</v>
+        <v>3.775043021218599</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.489198162117948</v>
+        <v>-5.454699066474581</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.553292547695012</v>
+        <v>1.567092185952359</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.1580637820993089</v>
+        <v>-0.08936482938363027</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.654489967596354</v>
+        <v>3.695709339225761</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462767</v>
+        <v>3.821044820462768</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.364717681393996</v>
+        <v>-5.33021858575063</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.602272450421023</v>
+        <v>1.616072088678369</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.1580637820993089</v>
+        <v>-0.08936482938363027</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.653677678032783</v>
+        <v>3.69489704966219</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533049</v>
+        <v>3.83232118453305</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.375102876283886</v>
+        <v>-5.340603780640519</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.607987151590139</v>
+        <v>1.621786789847486</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.1684489769891983</v>
+        <v>-0.09975002427351959</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.657315340223922</v>
+        <v>3.698534711853329</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.284348400255244</v>
+        <v>-5.249849304611877</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.715125947778021</v>
+        <v>1.728925586035368</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.07769450096055652</v>
+        <v>-0.00899554824487786</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.782605031617532</v>
+        <v>3.82382440324694</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.842771163672689</v>
+        <v>3.729293781699464</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.731243310712125</v>
+        <v>3.826090743012164</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.225928722718818</v>
+        <v>-5.127989201336901</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.640515397310851</v>
+        <v>1.774538638163657</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.01927482342413112</v>
+        <v>0.1128645550300978</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.719678416657647</v>
+        <v>3.893809476030223</v>
       </c>
     </row>
   </sheetData>
